--- a/app/src/test/resources/TestData/Pre-Order Meals APIs Test Cases.xlsx
+++ b/app/src/test/resources/TestData/Pre-Order Meals APIs Test Cases.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28125" windowHeight="12375"/>
+    <workbookView windowWidth="28125" windowHeight="12375" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Test Cases SET" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1298" uniqueCount="421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1072" uniqueCount="419">
   <si>
     <t>TC_ID</t>
   </si>
@@ -738,406 +738,400 @@
     <t>Item change cannot bypass lock</t>
   </si>
   <si>
-    <t>Expected Status / Code</t>
-  </si>
-  <si>
-    <t>Expected Result / Validation Message</t>
-  </si>
-  <si>
-    <t>Validation Basis</t>
-  </si>
-  <si>
     <t>TC099</t>
   </si>
   <si>
     <t>get</t>
   </si>
   <si>
-    <t>NOT SPECIFIED</t>
-  </si>
-  <si>
     <t>Get pre-order details with valid user-id</t>
   </si>
   <si>
+    <t>failed: 1210101003 : Incomplete command : date-range=</t>
+  </si>
+  <si>
+    <t>TC100</t>
+  </si>
+  <si>
+    <t>01062026-29082026</t>
+  </si>
+  <si>
+    <t>Valid user-id and date-range</t>
+  </si>
+  <si>
+    <t>success: 1210100000 : No records found</t>
+  </si>
+  <si>
+    <t>TC101</t>
+  </si>
+  <si>
+    <t>Omit date-range</t>
+  </si>
+  <si>
+    <t>TC102</t>
+  </si>
+  <si>
+    <t>15072026-15072026</t>
+  </si>
+  <si>
+    <t>Retrieve one-day data</t>
+  </si>
+  <si>
+    <t>TC103</t>
+  </si>
+  <si>
+    <t>90-day date range</t>
+  </si>
+  <si>
+    <t>TC104</t>
+  </si>
+  <si>
+    <t>01062026-30082026</t>
+  </si>
+  <si>
+    <t>91-day date range</t>
+  </si>
+  <si>
+    <t>TC105</t>
+  </si>
+  <si>
+    <t>60-day default validation</t>
+  </si>
+  <si>
+    <t>TC106</t>
+  </si>
+  <si>
+    <t>failed: 1210101003 : Incomplete command : user-id=</t>
+  </si>
+  <si>
+    <t>TC107</t>
+  </si>
+  <si>
+    <t>TC108</t>
+  </si>
+  <si>
+    <t>TC109</t>
+  </si>
+  <si>
+    <t>failed: 1210101004 : Invalid command : user-id=*</t>
+  </si>
+  <si>
+    <t>TC110</t>
+  </si>
+  <si>
+    <t>n1</t>
+  </si>
+  <si>
+    <t>TC111</t>
+  </si>
+  <si>
+    <t>User has no cafeteria rights</t>
+  </si>
+  <si>
+    <t>TC112</t>
+  </si>
+  <si>
+    <t>Invalid date-range format</t>
+  </si>
+  <si>
+    <t>failed: 1210101004 : Invalid command : date-range=malformed</t>
+  </si>
+  <si>
+    <t>TC113</t>
+  </si>
+  <si>
+    <t>Empty date-range</t>
+  </si>
+  <si>
+    <t>TC114</t>
+  </si>
+  <si>
+    <t>Invalid date-range syntax</t>
+  </si>
+  <si>
+    <t>TC115</t>
+  </si>
+  <si>
+    <t>02012020-01012020</t>
+  </si>
+  <si>
+    <t>From date greater than To date</t>
+  </si>
+  <si>
+    <t>failed: 1210103004 : From Date should be earlier than or equal to To Date</t>
+  </si>
+  <si>
+    <t>TC116</t>
+  </si>
+  <si>
+    <t>Only first date provided</t>
+  </si>
+  <si>
+    <t>failed: 1210101004 : Invalid command : date-range=1062026</t>
+  </si>
+  <si>
+    <t>TC117</t>
+  </si>
+  <si>
+    <t>Invalid parameter name</t>
+  </si>
+  <si>
+    <t>TC118</t>
+  </si>
+  <si>
+    <t>01012020-02012020</t>
+  </si>
+  <si>
+    <t>No data available</t>
+  </si>
+  <si>
+    <t>TC119</t>
+  </si>
+  <si>
+    <t>Missing action</t>
+  </si>
+  <si>
+    <t>failed: 1210001003 : Incomplete command : action=</t>
+  </si>
+  <si>
+    <t>TC121</t>
+  </si>
+  <si>
+    <t>Morethen15CharEMP123456789012</t>
+  </si>
+  <si>
+    <t>User-id maximum length</t>
+  </si>
+  <si>
+    <t>TC122</t>
+  </si>
+  <si>
+    <t>multiple</t>
+  </si>
+  <si>
+    <t>Multiple date ranges</t>
+  </si>
+  <si>
+    <t>failed: 1210101004 : Invalid command : date-range=multiple</t>
+  </si>
+  <si>
+    <t>TC123</t>
+  </si>
+  <si>
+    <t>special#$%user</t>
+  </si>
+  <si>
+    <t>Special characters in user-id</t>
+  </si>
+  <si>
+    <t>TC124</t>
+  </si>
+  <si>
+    <t>TC125</t>
+  </si>
+  <si>
+    <t>TC126</t>
+  </si>
+  <si>
+    <t>TC127</t>
+  </si>
+  <si>
+    <t>TC128</t>
+  </si>
+  <si>
+    <t>TC129</t>
+  </si>
+  <si>
+    <t>TC130</t>
+  </si>
+  <si>
+    <t>TC131</t>
+  </si>
+  <si>
+    <t>TC132</t>
+  </si>
+  <si>
+    <t>TC133</t>
+  </si>
+  <si>
+    <t>TC134</t>
+  </si>
+  <si>
+    <t>TC135</t>
+  </si>
+  <si>
+    <t>TC136</t>
+  </si>
+  <si>
+    <t>TC137</t>
+  </si>
+  <si>
+    <t>TC138</t>
+  </si>
+  <si>
+    <t>TC139</t>
+  </si>
+  <si>
+    <t>TC140</t>
+  </si>
+  <si>
+    <t>TC141</t>
+  </si>
+  <si>
+    <t>TC142</t>
+  </si>
+  <si>
+    <t>delete</t>
+  </si>
+  <si>
+    <t>Delete valid pre-order item</t>
+  </si>
+  <si>
     <t>GET/DELETE validation details are not included in the supplied story excerpt. Expected message/code must be taken from the corresponding GET/DELETE specification before asserting.</t>
   </si>
   <si>
-    <t>Not covered by supplied SET validation excerpt.</t>
-  </si>
-  <si>
-    <t>TC100</t>
-  </si>
-  <si>
-    <t>01062026-29082026</t>
-  </si>
-  <si>
-    <t>Valid user-id and date-range</t>
-  </si>
-  <si>
-    <t>TC101</t>
-  </si>
-  <si>
-    <t>Omit date-range</t>
-  </si>
-  <si>
-    <t>TC102</t>
-  </si>
-  <si>
-    <t>15072026-15072026</t>
-  </si>
-  <si>
-    <t>Retrieve one-day data</t>
-  </si>
-  <si>
-    <t>TC103</t>
-  </si>
-  <si>
-    <t>90-day date range</t>
-  </si>
-  <si>
-    <t>TC104</t>
-  </si>
-  <si>
-    <t>01062026-30082026</t>
-  </si>
-  <si>
-    <t>91-day date range</t>
-  </si>
-  <si>
-    <t>TC105</t>
-  </si>
-  <si>
-    <t>60-day default validation</t>
-  </si>
-  <si>
-    <t>TC106</t>
-  </si>
-  <si>
-    <t>TC107</t>
-  </si>
-  <si>
-    <t>TC108</t>
-  </si>
-  <si>
-    <t>TC109</t>
-  </si>
-  <si>
-    <t>TC110</t>
-  </si>
-  <si>
-    <t>n1</t>
-  </si>
-  <si>
-    <t>TC111</t>
-  </si>
-  <si>
-    <t>User has no cafeteria rights</t>
-  </si>
-  <si>
-    <t>TC112</t>
-  </si>
-  <si>
-    <t>Invalid date-range format</t>
-  </si>
-  <si>
-    <t>TC113</t>
-  </si>
-  <si>
-    <t>Empty date-range</t>
-  </si>
-  <si>
-    <t>TC114</t>
-  </si>
-  <si>
-    <t>Invalid date-range syntax</t>
-  </si>
-  <si>
-    <t>TC115</t>
-  </si>
-  <si>
-    <t>02012020-01012020</t>
-  </si>
-  <si>
-    <t>From date greater than To date</t>
-  </si>
-  <si>
-    <t>TC116</t>
-  </si>
-  <si>
-    <t>Only first date provided</t>
-  </si>
-  <si>
-    <t>TC117</t>
-  </si>
-  <si>
-    <t>Invalid parameter name</t>
-  </si>
-  <si>
-    <t>TC118</t>
-  </si>
-  <si>
-    <t>01012020-02012020</t>
-  </si>
-  <si>
-    <t>No data available</t>
-  </si>
-  <si>
-    <t>TC119</t>
-  </si>
-  <si>
-    <t>FAILED / INCOMPLETE COMMAND</t>
-  </si>
-  <si>
-    <t>Missing action</t>
-  </si>
-  <si>
-    <t>Incomplete command (action is mandatory; exact validation code/message not specified in supplied story)</t>
-  </si>
-  <si>
-    <t>TC120</t>
+    <t>TC143</t>
+  </si>
+  <si>
+    <t>Delete all items</t>
+  </si>
+  <si>
+    <t>TC144</t>
+  </si>
+  <si>
+    <t>Delete another valid menu item</t>
+  </si>
+  <si>
+    <t>TC145</t>
+  </si>
+  <si>
+    <t>Delete on restricted day</t>
+  </si>
+  <si>
+    <t>TC146</t>
+  </si>
+  <si>
+    <t>Maximum user-id length</t>
+  </si>
+  <si>
+    <t>TC147</t>
+  </si>
+  <si>
+    <t>TC148</t>
+  </si>
+  <si>
+    <t>TC149</t>
+  </si>
+  <si>
+    <t>TC150</t>
+  </si>
+  <si>
+    <t>TC151</t>
+  </si>
+  <si>
+    <t>TC152</t>
+  </si>
+  <si>
+    <t>User not enabled for Cafeteria</t>
+  </si>
+  <si>
+    <t>TC153</t>
+  </si>
+  <si>
+    <t>Pre-Order not enabled</t>
+  </si>
+  <si>
+    <t>TC154</t>
+  </si>
+  <si>
+    <t>TC155</t>
+  </si>
+  <si>
+    <t>Empty date</t>
+  </si>
+  <si>
+    <t>TC156</t>
+  </si>
+  <si>
+    <t>TC157</t>
+  </si>
+  <si>
+    <t>TC158</t>
+  </si>
+  <si>
+    <t>No pre-order exists</t>
+  </si>
+  <si>
+    <t>TC159</t>
+  </si>
+  <si>
+    <t>future</t>
+  </si>
+  <si>
+    <t>Outside allowed advance window</t>
+  </si>
+  <si>
+    <t>TC160</t>
+  </si>
+  <si>
+    <t>Previous/invalid date</t>
+  </si>
+  <si>
+    <t>TC161</t>
+  </si>
+  <si>
+    <t>restricted</t>
+  </si>
+  <si>
+    <t>TC162</t>
+  </si>
+  <si>
+    <t>TC163</t>
+  </si>
+  <si>
+    <t>TC164</t>
+  </si>
+  <si>
+    <t>TC165</t>
+  </si>
+  <si>
+    <t>TC166</t>
+  </si>
+  <si>
+    <t>TC167</t>
+  </si>
+  <si>
+    <t>TC168</t>
+  </si>
+  <si>
+    <t>TC169</t>
+  </si>
+  <si>
+    <t>TC170</t>
+  </si>
+  <si>
+    <t>Item not found in order</t>
+  </si>
+  <si>
+    <t>TC171</t>
+  </si>
+  <si>
+    <t>Item not available in selected menu</t>
+  </si>
+  <si>
+    <t>TC172</t>
+  </si>
+  <si>
+    <t>TC173</t>
+  </si>
+  <si>
+    <t>User already punched</t>
+  </si>
+  <si>
+    <t>TC174</t>
   </si>
   <si>
     <t>invalid</t>
-  </si>
-  <si>
-    <t>FAILED / INVALID REQUEST</t>
-  </si>
-  <si>
-    <t>Invalid action value</t>
-  </si>
-  <si>
-    <t>Invalid request</t>
-  </si>
-  <si>
-    <t>TC121</t>
-  </si>
-  <si>
-    <t>Morethen15CharEMP123456789012</t>
-  </si>
-  <si>
-    <t>User-id maximum length</t>
-  </si>
-  <si>
-    <t>TC122</t>
-  </si>
-  <si>
-    <t>multiple</t>
-  </si>
-  <si>
-    <t>Multiple date ranges</t>
-  </si>
-  <si>
-    <t>TC123</t>
-  </si>
-  <si>
-    <t>special#$%user</t>
-  </si>
-  <si>
-    <t>Special characters in user-id</t>
-  </si>
-  <si>
-    <t>TC124</t>
-  </si>
-  <si>
-    <t>TC125</t>
-  </si>
-  <si>
-    <t>TC126</t>
-  </si>
-  <si>
-    <t>TC127</t>
-  </si>
-  <si>
-    <t>TC128</t>
-  </si>
-  <si>
-    <t>TC129</t>
-  </si>
-  <si>
-    <t>TC130</t>
-  </si>
-  <si>
-    <t>TC131</t>
-  </si>
-  <si>
-    <t>TC132</t>
-  </si>
-  <si>
-    <t>TC133</t>
-  </si>
-  <si>
-    <t>TC134</t>
-  </si>
-  <si>
-    <t>TC135</t>
-  </si>
-  <si>
-    <t>TC136</t>
-  </si>
-  <si>
-    <t>TC137</t>
-  </si>
-  <si>
-    <t>TC138</t>
-  </si>
-  <si>
-    <t>TC139</t>
-  </si>
-  <si>
-    <t>TC140</t>
-  </si>
-  <si>
-    <t>TC141</t>
-  </si>
-  <si>
-    <t>TC142</t>
-  </si>
-  <si>
-    <t>delete</t>
-  </si>
-  <si>
-    <t>Delete valid pre-order item</t>
-  </si>
-  <si>
-    <t>TC143</t>
-  </si>
-  <si>
-    <t>Delete all items</t>
-  </si>
-  <si>
-    <t>TC144</t>
-  </si>
-  <si>
-    <t>Delete another valid menu item</t>
-  </si>
-  <si>
-    <t>TC145</t>
-  </si>
-  <si>
-    <t>Delete on restricted day</t>
-  </si>
-  <si>
-    <t>TC146</t>
-  </si>
-  <si>
-    <t>Maximum user-id length</t>
-  </si>
-  <si>
-    <t>TC147</t>
-  </si>
-  <si>
-    <t>TC148</t>
-  </si>
-  <si>
-    <t>TC149</t>
-  </si>
-  <si>
-    <t>TC150</t>
-  </si>
-  <si>
-    <t>TC151</t>
-  </si>
-  <si>
-    <t>TC152</t>
-  </si>
-  <si>
-    <t>User not enabled for Cafeteria</t>
-  </si>
-  <si>
-    <t>TC153</t>
-  </si>
-  <si>
-    <t>Pre-Order not enabled</t>
-  </si>
-  <si>
-    <t>TC154</t>
-  </si>
-  <si>
-    <t>TC155</t>
-  </si>
-  <si>
-    <t>Empty date</t>
-  </si>
-  <si>
-    <t>TC156</t>
-  </si>
-  <si>
-    <t>TC157</t>
-  </si>
-  <si>
-    <t>TC158</t>
-  </si>
-  <si>
-    <t>No pre-order exists</t>
-  </si>
-  <si>
-    <t>TC159</t>
-  </si>
-  <si>
-    <t>future</t>
-  </si>
-  <si>
-    <t>Outside allowed advance window</t>
-  </si>
-  <si>
-    <t>TC160</t>
-  </si>
-  <si>
-    <t>Previous/invalid date</t>
-  </si>
-  <si>
-    <t>TC161</t>
-  </si>
-  <si>
-    <t>restricted</t>
-  </si>
-  <si>
-    <t>TC162</t>
-  </si>
-  <si>
-    <t>TC163</t>
-  </si>
-  <si>
-    <t>TC164</t>
-  </si>
-  <si>
-    <t>TC165</t>
-  </si>
-  <si>
-    <t>TC166</t>
-  </si>
-  <si>
-    <t>TC167</t>
-  </si>
-  <si>
-    <t>TC168</t>
-  </si>
-  <si>
-    <t>TC169</t>
-  </si>
-  <si>
-    <t>TC170</t>
-  </si>
-  <si>
-    <t>Item not found in order</t>
-  </si>
-  <si>
-    <t>TC171</t>
-  </si>
-  <si>
-    <t>Item not available in selected menu</t>
-  </si>
-  <si>
-    <t>TC172</t>
-  </si>
-  <si>
-    <t>TC173</t>
-  </si>
-  <si>
-    <t>User already punched</t>
-  </si>
-  <si>
-    <t>TC174</t>
   </si>
   <si>
     <t>Invalid action</t>
@@ -1289,12 +1283,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ &quot;₹&quot;* #,##0.00_ ;_ &quot;₹&quot;* \-#,##0.00_ ;_ &quot;₹&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0.00_ ;_ &quot;₹&quot;* \-#,##0.00_ ;_ &quot;₹&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1319,6 +1313,18 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
@@ -1327,8 +1333,29 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="15"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -1343,22 +1370,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="13"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -1373,6 +1386,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
@@ -1381,15 +1401,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="18"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -1405,17 +1418,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1426,9 +1432,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1456,20 +1476,6 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -1477,6 +1483,12 @@
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1492,31 +1504,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1528,13 +1522,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1552,43 +1564,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1600,37 +1594,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1648,19 +1618,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1693,7 +1699,16 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1713,6 +1728,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -1724,15 +1748,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1777,15 +1792,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1795,146 +1801,146 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="3">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="7">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2">
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="4">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="9">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0">
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="7">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2">
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="22" borderId="6">
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0">
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0">
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1948,6 +1954,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1955,7 +1969,7 @@
     <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -2291,7 +2305,7 @@
     <col min="7" max="7" width="10.5714285714286" style="1" customWidth="1"/>
     <col min="8" max="8" width="9.28571428571429" style="1" customWidth="1"/>
     <col min="9" max="9" width="28" style="4" customWidth="1"/>
-    <col min="10" max="10" width="30" style="6" customWidth="1"/>
+    <col min="10" max="10" width="30" style="10" customWidth="1"/>
     <col min="11" max="16381" width="80" style="1" customWidth="1"/>
     <col min="16382" max="16382" width="80" style="1"/>
     <col min="16383" max="16384" width="33" style="1"/>
@@ -2325,7 +2339,7 @@
       <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="12" t="s">
         <v>9</v>
       </c>
     </row>
@@ -2354,7 +2368,7 @@
       <c r="I2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="J2" s="9" t="s">
+      <c r="J2" s="13" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2383,7 +2397,7 @@
       <c r="I3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="J3" s="13" t="s">
         <v>17</v>
       </c>
     </row>
@@ -2412,7 +2426,7 @@
       <c r="I4" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="J4" s="9" t="s">
+      <c r="J4" s="13" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2441,7 +2455,7 @@
       <c r="I5" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="J5" s="9" t="s">
+      <c r="J5" s="13" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2470,7 +2484,7 @@
       <c r="I6" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="J6" s="9" t="s">
+      <c r="J6" s="13" t="s">
         <v>26</v>
       </c>
     </row>
@@ -2499,7 +2513,7 @@
       <c r="I7" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="J7" s="9" t="s">
+      <c r="J7" s="13" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2528,7 +2542,7 @@
       <c r="I8" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="J8" s="9" t="s">
+      <c r="J8" s="13" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2557,7 +2571,7 @@
       <c r="I9" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="J9" s="9" t="s">
+      <c r="J9" s="13" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2577,7 +2591,7 @@
       <c r="E10" s="1">
         <v>1</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="11">
         <v>1129</v>
       </c>
       <c r="G10" s="1">
@@ -2586,7 +2600,7 @@
       <c r="I10" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="J10" s="9" t="s">
+      <c r="J10" s="13" t="s">
         <v>35</v>
       </c>
     </row>
@@ -2615,7 +2629,7 @@
       <c r="I11" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="J11" s="9" t="s">
+      <c r="J11" s="13" t="s">
         <v>38</v>
       </c>
     </row>
@@ -2644,7 +2658,7 @@
       <c r="I12" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="J12" s="9" t="s">
+      <c r="J12" s="13" t="s">
         <v>38</v>
       </c>
     </row>
@@ -2673,7 +2687,7 @@
       <c r="I13" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="J13" s="9" t="s">
+      <c r="J13" s="13" t="s">
         <v>38</v>
       </c>
     </row>
@@ -2702,7 +2716,7 @@
       <c r="I14" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="J14" s="9" t="s">
+      <c r="J14" s="13" t="s">
         <v>38</v>
       </c>
     </row>
@@ -2731,7 +2745,7 @@
       <c r="I15" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="J15" s="9" t="s">
+      <c r="J15" s="13" t="s">
         <v>38</v>
       </c>
     </row>
@@ -2760,7 +2774,7 @@
       <c r="I16" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="J16" s="9" t="s">
+      <c r="J16" s="13" t="s">
         <v>38</v>
       </c>
     </row>
@@ -2789,7 +2803,7 @@
       <c r="I17" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="J17" s="9" t="s">
+      <c r="J17" s="13" t="s">
         <v>38</v>
       </c>
     </row>
@@ -2816,7 +2830,7 @@
       <c r="I18" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="J18" s="9" t="s">
+      <c r="J18" s="13" t="s">
         <v>53</v>
       </c>
     </row>
@@ -2843,7 +2857,7 @@
       <c r="I19" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="J19" s="9" t="s">
+      <c r="J19" s="13" t="s">
         <v>53</v>
       </c>
     </row>
@@ -2872,7 +2886,7 @@
       <c r="I20" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="J20" s="9" t="s">
+      <c r="J20" s="13" t="s">
         <v>59</v>
       </c>
     </row>
@@ -2901,7 +2915,7 @@
       <c r="I21" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="J21" s="9" t="s">
+      <c r="J21" s="13" t="s">
         <v>63</v>
       </c>
     </row>
@@ -2930,7 +2944,7 @@
       <c r="I22" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="J22" s="9" t="s">
+      <c r="J22" s="13" t="s">
         <v>59</v>
       </c>
     </row>
@@ -2959,7 +2973,7 @@
       <c r="I23" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="J23" s="9" t="s">
+      <c r="J23" s="13" t="s">
         <v>59</v>
       </c>
     </row>
@@ -2988,7 +3002,7 @@
       <c r="I24" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="J24" s="9" t="s">
+      <c r="J24" s="13" t="s">
         <v>26</v>
       </c>
     </row>
@@ -3017,7 +3031,7 @@
       <c r="I25" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="J25" s="9" t="s">
+      <c r="J25" s="13" t="s">
         <v>38</v>
       </c>
     </row>
@@ -3044,7 +3058,7 @@
       <c r="I26" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="J26" s="9" t="s">
+      <c r="J26" s="13" t="s">
         <v>76</v>
       </c>
     </row>
@@ -3073,7 +3087,7 @@
       <c r="I27" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="J27" s="9" t="s">
+      <c r="J27" s="13" t="s">
         <v>79</v>
       </c>
     </row>
@@ -3102,7 +3116,7 @@
       <c r="I28" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="J28" s="9" t="s">
+      <c r="J28" s="13" t="s">
         <v>82</v>
       </c>
     </row>
@@ -3131,7 +3145,7 @@
       <c r="I29" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="J29" s="9" t="s">
+      <c r="J29" s="13" t="s">
         <v>85</v>
       </c>
     </row>
@@ -3160,7 +3174,7 @@
       <c r="I30" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="J30" s="9" t="s">
+      <c r="J30" s="13" t="s">
         <v>88</v>
       </c>
     </row>
@@ -3189,7 +3203,7 @@
       <c r="I31" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="J31" s="9" t="s">
+      <c r="J31" s="13" t="s">
         <v>17</v>
       </c>
     </row>
@@ -3218,7 +3232,7 @@
       <c r="I32" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="J32" s="9" t="s">
+      <c r="J32" s="13" t="s">
         <v>93</v>
       </c>
     </row>
@@ -3247,7 +3261,7 @@
       <c r="I33" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="J33" s="9" t="s">
+      <c r="J33" s="13" t="s">
         <v>96</v>
       </c>
     </row>
@@ -3273,7 +3287,7 @@
       <c r="I34" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="J34" s="9" t="s">
+      <c r="J34" s="13" t="s">
         <v>99</v>
       </c>
     </row>
@@ -3299,7 +3313,7 @@
       <c r="I35" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="J35" s="9" t="s">
+      <c r="J35" s="13" t="s">
         <v>99</v>
       </c>
     </row>
@@ -3328,7 +3342,7 @@
       <c r="I36" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="J36" s="9" t="s">
+      <c r="J36" s="13" t="s">
         <v>96</v>
       </c>
     </row>
@@ -3357,7 +3371,7 @@
       <c r="I37" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="J37" s="9" t="s">
+      <c r="J37" s="13" t="s">
         <v>105</v>
       </c>
     </row>
@@ -3386,7 +3400,7 @@
       <c r="I38" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="J38" s="9" t="s">
+      <c r="J38" s="13" t="s">
         <v>108</v>
       </c>
     </row>
@@ -3415,7 +3429,7 @@
       <c r="I39" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="J39" s="9" t="s">
+      <c r="J39" s="13" t="s">
         <v>108</v>
       </c>
     </row>
@@ -3444,7 +3458,7 @@
       <c r="I40" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="J40" s="9" t="s">
+      <c r="J40" s="13" t="s">
         <v>113</v>
       </c>
     </row>
@@ -3473,7 +3487,7 @@
       <c r="I41" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="J41" s="9" t="s">
+      <c r="J41" s="13" t="s">
         <v>117</v>
       </c>
     </row>
@@ -3502,7 +3516,7 @@
       <c r="I42" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="J42" s="9" t="s">
+      <c r="J42" s="13" t="s">
         <v>117</v>
       </c>
     </row>
@@ -3531,7 +3545,7 @@
       <c r="I43" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="J43" s="9" t="s">
+      <c r="J43" s="13" t="s">
         <v>113</v>
       </c>
     </row>
@@ -3560,7 +3574,7 @@
       <c r="I44" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="J44" s="9" t="s">
+      <c r="J44" s="13" t="s">
         <v>123</v>
       </c>
     </row>
@@ -3587,7 +3601,7 @@
       <c r="I45" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="J45" s="9" t="s">
+      <c r="J45" s="13" t="s">
         <v>126</v>
       </c>
     </row>
@@ -3614,7 +3628,7 @@
       <c r="I46" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="J46" s="9" t="s">
+      <c r="J46" s="13" t="s">
         <v>126</v>
       </c>
     </row>
@@ -3643,7 +3657,7 @@
       <c r="I47" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="J47" s="9" t="s">
+      <c r="J47" s="13" t="s">
         <v>131</v>
       </c>
     </row>
@@ -3672,7 +3686,7 @@
       <c r="I48" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="J48" s="9" t="s">
+      <c r="J48" s="13" t="s">
         <v>134</v>
       </c>
     </row>
@@ -3701,7 +3715,7 @@
       <c r="I49" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="J49" s="9" t="s">
+      <c r="J49" s="13" t="s">
         <v>137</v>
       </c>
     </row>
@@ -3730,7 +3744,7 @@
       <c r="I50" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="J50" s="9" t="s">
+      <c r="J50" s="13" t="s">
         <v>38</v>
       </c>
     </row>
@@ -3759,7 +3773,7 @@
       <c r="I51" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="J51" s="9" t="s">
+      <c r="J51" s="13" t="s">
         <v>142</v>
       </c>
     </row>
@@ -3788,7 +3802,7 @@
       <c r="I52" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="J52" s="9" t="s">
+      <c r="J52" s="13" t="s">
         <v>146</v>
       </c>
     </row>
@@ -3817,7 +3831,7 @@
       <c r="I53" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="J53" s="9" t="s">
+      <c r="J53" s="13" t="s">
         <v>149</v>
       </c>
     </row>
@@ -3846,7 +3860,7 @@
       <c r="I54" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="J54" s="9" t="s">
+      <c r="J54" s="13" t="s">
         <v>38</v>
       </c>
     </row>
@@ -3875,7 +3889,7 @@
       <c r="I55" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="J55" s="9" t="s">
+      <c r="J55" s="13" t="s">
         <v>38</v>
       </c>
     </row>
@@ -3904,7 +3918,7 @@
       <c r="I56" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="J56" s="9" t="s">
+      <c r="J56" s="13" t="s">
         <v>38</v>
       </c>
     </row>
@@ -3933,7 +3947,7 @@
       <c r="I57" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="J57" s="9" t="s">
+      <c r="J57" s="13" t="s">
         <v>38</v>
       </c>
     </row>
@@ -3962,7 +3976,7 @@
       <c r="I58" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="J58" s="9" t="s">
+      <c r="J58" s="13" t="s">
         <v>38</v>
       </c>
     </row>
@@ -3991,7 +4005,7 @@
       <c r="I59" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="J59" s="9" t="s">
+      <c r="J59" s="13" t="s">
         <v>38</v>
       </c>
     </row>
@@ -4020,7 +4034,7 @@
       <c r="I60" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="J60" s="9" t="s">
+      <c r="J60" s="13" t="s">
         <v>38</v>
       </c>
     </row>
@@ -4049,7 +4063,7 @@
       <c r="I61" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="J61" s="9" t="s">
+      <c r="J61" s="13" t="s">
         <v>38</v>
       </c>
     </row>
@@ -4078,7 +4092,7 @@
       <c r="I62" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="J62" s="9" t="s">
+      <c r="J62" s="13" t="s">
         <v>38</v>
       </c>
     </row>
@@ -4107,7 +4121,7 @@
       <c r="I63" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="J63" s="9" t="s">
+      <c r="J63" s="13" t="s">
         <v>38</v>
       </c>
     </row>
@@ -4136,7 +4150,7 @@
       <c r="I64" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="J64" s="9" t="s">
+      <c r="J64" s="13" t="s">
         <v>38</v>
       </c>
     </row>
@@ -4165,7 +4179,7 @@
       <c r="I65" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="J65" s="9" t="s">
+      <c r="J65" s="13" t="s">
         <v>88</v>
       </c>
     </row>
@@ -4194,7 +4208,7 @@
       <c r="I66" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="J66" s="9" t="s">
+      <c r="J66" s="13" t="s">
         <v>38</v>
       </c>
     </row>
@@ -4223,7 +4237,7 @@
       <c r="I67" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="J67" s="9" t="s">
+      <c r="J67" s="13" t="s">
         <v>38</v>
       </c>
     </row>
@@ -4252,7 +4266,7 @@
       <c r="I68" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="J68" s="9" t="s">
+      <c r="J68" s="13" t="s">
         <v>38</v>
       </c>
     </row>
@@ -4281,7 +4295,7 @@
       <c r="I69" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="J69" s="9" t="s">
+      <c r="J69" s="13" t="s">
         <v>38</v>
       </c>
     </row>
@@ -4310,7 +4324,7 @@
       <c r="I70" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="J70" s="9" t="s">
+      <c r="J70" s="13" t="s">
         <v>38</v>
       </c>
     </row>
@@ -4339,7 +4353,7 @@
       <c r="I71" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="J71" s="9" t="s">
+      <c r="J71" s="13" t="s">
         <v>134</v>
       </c>
     </row>
@@ -4368,7 +4382,7 @@
       <c r="I72" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="J72" s="9" t="s">
+      <c r="J72" s="13" t="s">
         <v>38</v>
       </c>
     </row>
@@ -4397,7 +4411,7 @@
       <c r="I73" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="J73" s="9" t="s">
+      <c r="J73" s="13" t="s">
         <v>38</v>
       </c>
     </row>
@@ -4426,7 +4440,7 @@
       <c r="I74" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="J74" s="9" t="s">
+      <c r="J74" s="13" t="s">
         <v>38</v>
       </c>
     </row>
@@ -4455,7 +4469,7 @@
       <c r="I75" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="J75" s="9" t="s">
+      <c r="J75" s="13" t="s">
         <v>38</v>
       </c>
     </row>
@@ -4484,7 +4498,7 @@
       <c r="I76" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="J76" s="9" t="s">
+      <c r="J76" s="13" t="s">
         <v>38</v>
       </c>
     </row>
@@ -4513,7 +4527,7 @@
       <c r="I77" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="J77" s="9" t="s">
+      <c r="J77" s="13" t="s">
         <v>38</v>
       </c>
     </row>
@@ -4542,7 +4556,7 @@
       <c r="I78" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="J78" s="9" t="s">
+      <c r="J78" s="13" t="s">
         <v>59</v>
       </c>
     </row>
@@ -4571,7 +4585,7 @@
       <c r="I79" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="J79" s="9" t="s">
+      <c r="J79" s="13" t="s">
         <v>59</v>
       </c>
     </row>
@@ -4600,7 +4614,7 @@
       <c r="I80" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="J80" s="9" t="s">
+      <c r="J80" s="13" t="s">
         <v>59</v>
       </c>
     </row>
@@ -4629,7 +4643,7 @@
       <c r="I81" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="J81" s="9" t="s">
+      <c r="J81" s="13" t="s">
         <v>38</v>
       </c>
     </row>
@@ -4658,7 +4672,7 @@
       <c r="I82" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="J82" s="9" t="s">
+      <c r="J82" s="13" t="s">
         <v>38</v>
       </c>
     </row>
@@ -4687,7 +4701,7 @@
       <c r="I83" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="J83" s="9" t="s">
+      <c r="J83" s="13" t="s">
         <v>38</v>
       </c>
     </row>
@@ -4716,7 +4730,7 @@
       <c r="I84" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="J84" s="9" t="s">
+      <c r="J84" s="13" t="s">
         <v>38</v>
       </c>
     </row>
@@ -4745,7 +4759,7 @@
       <c r="I85" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="J85" s="9" t="s">
+      <c r="J85" s="13" t="s">
         <v>38</v>
       </c>
     </row>
@@ -4774,7 +4788,7 @@
       <c r="I86" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="J86" s="9" t="s">
+      <c r="J86" s="13" t="s">
         <v>38</v>
       </c>
     </row>
@@ -4803,7 +4817,7 @@
       <c r="I87" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="J87" s="9" t="s">
+      <c r="J87" s="13" t="s">
         <v>38</v>
       </c>
     </row>
@@ -4832,7 +4846,7 @@
       <c r="I88" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="J88" s="9" t="s">
+      <c r="J88" s="13" t="s">
         <v>38</v>
       </c>
     </row>
@@ -4861,7 +4875,7 @@
       <c r="I89" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="J89" s="9" t="s">
+      <c r="J89" s="13" t="s">
         <v>38</v>
       </c>
     </row>
@@ -4890,7 +4904,7 @@
       <c r="I90" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="J90" s="9" t="s">
+      <c r="J90" s="13" t="s">
         <v>38</v>
       </c>
     </row>
@@ -4919,7 +4933,7 @@
       <c r="I91" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="J91" s="9" t="s">
+      <c r="J91" s="13" t="s">
         <v>38</v>
       </c>
     </row>
@@ -4948,7 +4962,7 @@
       <c r="I92" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="J92" s="9" t="s">
+      <c r="J92" s="13" t="s">
         <v>38</v>
       </c>
     </row>
@@ -4977,7 +4991,7 @@
       <c r="I93" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="J93" s="9" t="s">
+      <c r="J93" s="13" t="s">
         <v>38</v>
       </c>
     </row>
@@ -5006,7 +5020,7 @@
       <c r="I94" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="J94" s="9" t="s">
+      <c r="J94" s="13" t="s">
         <v>38</v>
       </c>
     </row>
@@ -5035,7 +5049,7 @@
       <c r="I95" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="J95" s="9" t="s">
+      <c r="J95" s="13" t="s">
         <v>38</v>
       </c>
     </row>
@@ -5064,7 +5078,7 @@
       <c r="I96" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="J96" s="9" t="s">
+      <c r="J96" s="13" t="s">
         <v>38</v>
       </c>
     </row>
@@ -5093,7 +5107,7 @@
       <c r="I97" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="J97" s="9" t="s">
+      <c r="J97" s="13" t="s">
         <v>38</v>
       </c>
     </row>
@@ -5122,7 +5136,7 @@
       <c r="I98" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="J98" s="9" t="s">
+      <c r="J98" s="13" t="s">
         <v>38</v>
       </c>
     </row>
@@ -5151,204 +5165,204 @@
       <c r="I99" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="J99" s="9" t="s">
+      <c r="J99" s="13" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="100" s="5" customFormat="1" ht="15" spans="10:10">
-      <c r="J100" s="6"/>
-    </row>
-    <row r="101" s="5" customFormat="1" ht="15" spans="10:10">
-      <c r="J101" s="6"/>
-    </row>
-    <row r="102" s="5" customFormat="1" ht="15" spans="10:10">
-      <c r="J102" s="6"/>
-    </row>
-    <row r="103" s="5" customFormat="1" ht="15" spans="10:10">
-      <c r="J103" s="6"/>
-    </row>
-    <row r="104" s="5" customFormat="1" ht="15" spans="10:10">
-      <c r="J104" s="6"/>
-    </row>
-    <row r="105" s="5" customFormat="1" ht="15" spans="10:10">
-      <c r="J105" s="6"/>
-    </row>
-    <row r="106" s="5" customFormat="1" ht="15" spans="10:10">
-      <c r="J106" s="6"/>
-    </row>
-    <row r="107" s="5" customFormat="1" ht="15" spans="10:10">
-      <c r="J107" s="6"/>
-    </row>
-    <row r="108" s="5" customFormat="1" ht="15" spans="10:10">
-      <c r="J108" s="6"/>
-    </row>
-    <row r="109" s="5" customFormat="1" ht="15" spans="10:10">
-      <c r="J109" s="6"/>
-    </row>
-    <row r="110" s="5" customFormat="1" ht="15" spans="10:10">
-      <c r="J110" s="6"/>
-    </row>
-    <row r="111" s="5" customFormat="1" ht="15" spans="10:10">
-      <c r="J111" s="6"/>
-    </row>
-    <row r="112" s="5" customFormat="1" ht="15" spans="10:10">
-      <c r="J112" s="6"/>
-    </row>
-    <row r="113" s="5" customFormat="1" ht="15" spans="10:10">
-      <c r="J113" s="6"/>
-    </row>
-    <row r="114" s="5" customFormat="1" ht="15" spans="10:10">
-      <c r="J114" s="6"/>
-    </row>
-    <row r="115" s="5" customFormat="1" ht="15" spans="10:10">
-      <c r="J115" s="6"/>
-    </row>
-    <row r="116" s="5" customFormat="1" ht="15" spans="10:10">
-      <c r="J116" s="6"/>
-    </row>
-    <row r="117" s="5" customFormat="1" ht="15" spans="10:10">
-      <c r="J117" s="6"/>
-    </row>
-    <row r="118" s="5" customFormat="1" ht="15" spans="10:10">
-      <c r="J118" s="6"/>
-    </row>
-    <row r="119" s="5" customFormat="1" ht="15" spans="10:10">
-      <c r="J119" s="6"/>
-    </row>
-    <row r="120" s="5" customFormat="1" ht="15" spans="10:10">
-      <c r="J120" s="6"/>
-    </row>
-    <row r="121" s="5" customFormat="1" ht="15" spans="10:10">
-      <c r="J121" s="6"/>
-    </row>
-    <row r="122" s="5" customFormat="1" ht="15" spans="10:10">
-      <c r="J122" s="6"/>
-    </row>
-    <row r="123" s="5" customFormat="1" ht="15" spans="10:10">
-      <c r="J123" s="6"/>
-    </row>
-    <row r="124" s="5" customFormat="1" ht="15" spans="10:10">
-      <c r="J124" s="6"/>
-    </row>
-    <row r="125" s="5" customFormat="1" ht="15" spans="10:10">
-      <c r="J125" s="6"/>
-    </row>
-    <row r="126" s="5" customFormat="1" ht="15" spans="10:10">
-      <c r="J126" s="6"/>
-    </row>
-    <row r="127" s="5" customFormat="1" ht="15" spans="10:10">
-      <c r="J127" s="6"/>
-    </row>
-    <row r="128" s="5" customFormat="1" ht="15" spans="10:10">
-      <c r="J128" s="6"/>
-    </row>
-    <row r="129" s="5" customFormat="1" ht="15" spans="10:10">
-      <c r="J129" s="6"/>
-    </row>
-    <row r="130" s="5" customFormat="1" ht="15" spans="10:10">
-      <c r="J130" s="6"/>
-    </row>
-    <row r="131" s="5" customFormat="1" ht="15" spans="10:10">
-      <c r="J131" s="6"/>
-    </row>
-    <row r="132" s="5" customFormat="1" ht="15" spans="10:10">
-      <c r="J132" s="6"/>
-    </row>
-    <row r="133" s="5" customFormat="1" ht="15" spans="10:10">
-      <c r="J133" s="6"/>
-    </row>
-    <row r="134" s="5" customFormat="1" ht="15" spans="10:10">
-      <c r="J134" s="6"/>
-    </row>
-    <row r="135" s="5" customFormat="1" ht="15" spans="10:10">
-      <c r="J135" s="6"/>
-    </row>
-    <row r="136" s="5" customFormat="1" ht="15" spans="10:10">
-      <c r="J136" s="6"/>
-    </row>
-    <row r="137" s="5" customFormat="1" ht="15" spans="10:10">
-      <c r="J137" s="6"/>
-    </row>
-    <row r="138" s="5" customFormat="1" ht="15" spans="10:10">
-      <c r="J138" s="6"/>
-    </row>
-    <row r="139" s="5" customFormat="1" ht="15" spans="10:10">
-      <c r="J139" s="6"/>
-    </row>
-    <row r="140" s="5" customFormat="1" ht="15" spans="10:10">
-      <c r="J140" s="6"/>
-    </row>
-    <row r="141" s="5" customFormat="1" ht="15" spans="10:10">
-      <c r="J141" s="6"/>
-    </row>
-    <row r="142" s="5" customFormat="1" ht="15" spans="10:10">
-      <c r="J142" s="6"/>
-    </row>
-    <row r="143" s="5" customFormat="1" ht="15" spans="10:10">
-      <c r="J143" s="6"/>
-    </row>
-    <row r="144" s="5" customFormat="1" ht="15" spans="10:10">
-      <c r="J144" s="6"/>
-    </row>
-    <row r="145" s="5" customFormat="1" ht="15" spans="10:10">
-      <c r="J145" s="6"/>
-    </row>
-    <row r="146" s="5" customFormat="1" ht="15" spans="10:10">
-      <c r="J146" s="6"/>
-    </row>
-    <row r="147" s="5" customFormat="1" ht="15" spans="10:10">
-      <c r="J147" s="6"/>
-    </row>
-    <row r="148" s="5" customFormat="1" ht="15" spans="10:10">
-      <c r="J148" s="6"/>
-    </row>
-    <row r="149" s="5" customFormat="1" ht="15" spans="10:10">
-      <c r="J149" s="6"/>
-    </row>
-    <row r="150" s="5" customFormat="1" ht="15" spans="10:10">
-      <c r="J150" s="6"/>
-    </row>
-    <row r="151" s="5" customFormat="1" ht="15" spans="10:10">
-      <c r="J151" s="6"/>
-    </row>
-    <row r="152" s="5" customFormat="1" ht="15" spans="10:10">
-      <c r="J152" s="6"/>
-    </row>
-    <row r="153" s="5" customFormat="1" ht="15" spans="10:10">
-      <c r="J153" s="6"/>
-    </row>
-    <row r="154" s="5" customFormat="1" ht="15" spans="10:10">
-      <c r="J154" s="6"/>
-    </row>
-    <row r="155" s="5" customFormat="1" ht="15" spans="10:10">
-      <c r="J155" s="6"/>
-    </row>
-    <row r="156" s="5" customFormat="1" ht="15" spans="10:10">
-      <c r="J156" s="6"/>
-    </row>
-    <row r="157" s="5" customFormat="1" ht="15" spans="10:10">
-      <c r="J157" s="6"/>
-    </row>
-    <row r="158" s="5" customFormat="1" ht="15" spans="10:10">
-      <c r="J158" s="6"/>
-    </row>
-    <row r="159" s="5" customFormat="1" ht="15" spans="10:10">
-      <c r="J159" s="6"/>
-    </row>
-    <row r="160" s="5" customFormat="1" ht="15" spans="10:10">
-      <c r="J160" s="6"/>
-    </row>
-    <row r="161" s="5" customFormat="1" ht="15" spans="10:10">
-      <c r="J161" s="6"/>
-    </row>
-    <row r="162" s="5" customFormat="1" ht="15" spans="10:10">
-      <c r="J162" s="6"/>
-    </row>
-    <row r="163" s="5" customFormat="1" ht="15" spans="10:10">
-      <c r="J163" s="6"/>
-    </row>
-    <row r="164" s="5" customFormat="1" ht="15" spans="10:10">
-      <c r="J164" s="6"/>
+    <row r="100" s="9" customFormat="1" ht="15" spans="10:10">
+      <c r="J100" s="10"/>
+    </row>
+    <row r="101" s="9" customFormat="1" ht="15" spans="10:10">
+      <c r="J101" s="10"/>
+    </row>
+    <row r="102" s="9" customFormat="1" ht="15" spans="10:10">
+      <c r="J102" s="10"/>
+    </row>
+    <row r="103" s="9" customFormat="1" ht="15" spans="10:10">
+      <c r="J103" s="10"/>
+    </row>
+    <row r="104" s="9" customFormat="1" ht="15" spans="10:10">
+      <c r="J104" s="10"/>
+    </row>
+    <row r="105" s="9" customFormat="1" ht="15" spans="10:10">
+      <c r="J105" s="10"/>
+    </row>
+    <row r="106" s="9" customFormat="1" ht="15" spans="10:10">
+      <c r="J106" s="10"/>
+    </row>
+    <row r="107" s="9" customFormat="1" ht="15" spans="10:10">
+      <c r="J107" s="10"/>
+    </row>
+    <row r="108" s="9" customFormat="1" ht="15" spans="10:10">
+      <c r="J108" s="10"/>
+    </row>
+    <row r="109" s="9" customFormat="1" ht="15" spans="10:10">
+      <c r="J109" s="10"/>
+    </row>
+    <row r="110" s="9" customFormat="1" ht="15" spans="10:10">
+      <c r="J110" s="10"/>
+    </row>
+    <row r="111" s="9" customFormat="1" ht="15" spans="10:10">
+      <c r="J111" s="10"/>
+    </row>
+    <row r="112" s="9" customFormat="1" ht="15" spans="10:10">
+      <c r="J112" s="10"/>
+    </row>
+    <row r="113" s="9" customFormat="1" ht="15" spans="10:10">
+      <c r="J113" s="10"/>
+    </row>
+    <row r="114" s="9" customFormat="1" ht="15" spans="10:10">
+      <c r="J114" s="10"/>
+    </row>
+    <row r="115" s="9" customFormat="1" ht="15" spans="10:10">
+      <c r="J115" s="10"/>
+    </row>
+    <row r="116" s="9" customFormat="1" ht="15" spans="10:10">
+      <c r="J116" s="10"/>
+    </row>
+    <row r="117" s="9" customFormat="1" ht="15" spans="10:10">
+      <c r="J117" s="10"/>
+    </row>
+    <row r="118" s="9" customFormat="1" ht="15" spans="10:10">
+      <c r="J118" s="10"/>
+    </row>
+    <row r="119" s="9" customFormat="1" ht="15" spans="10:10">
+      <c r="J119" s="10"/>
+    </row>
+    <row r="120" s="9" customFormat="1" ht="15" spans="10:10">
+      <c r="J120" s="10"/>
+    </row>
+    <row r="121" s="9" customFormat="1" ht="15" spans="10:10">
+      <c r="J121" s="10"/>
+    </row>
+    <row r="122" s="9" customFormat="1" ht="15" spans="10:10">
+      <c r="J122" s="10"/>
+    </row>
+    <row r="123" s="9" customFormat="1" ht="15" spans="10:10">
+      <c r="J123" s="10"/>
+    </row>
+    <row r="124" s="9" customFormat="1" ht="15" spans="10:10">
+      <c r="J124" s="10"/>
+    </row>
+    <row r="125" s="9" customFormat="1" ht="15" spans="10:10">
+      <c r="J125" s="10"/>
+    </row>
+    <row r="126" s="9" customFormat="1" ht="15" spans="10:10">
+      <c r="J126" s="10"/>
+    </row>
+    <row r="127" s="9" customFormat="1" ht="15" spans="10:10">
+      <c r="J127" s="10"/>
+    </row>
+    <row r="128" s="9" customFormat="1" ht="15" spans="10:10">
+      <c r="J128" s="10"/>
+    </row>
+    <row r="129" s="9" customFormat="1" ht="15" spans="10:10">
+      <c r="J129" s="10"/>
+    </row>
+    <row r="130" s="9" customFormat="1" ht="15" spans="10:10">
+      <c r="J130" s="10"/>
+    </row>
+    <row r="131" s="9" customFormat="1" ht="15" spans="10:10">
+      <c r="J131" s="10"/>
+    </row>
+    <row r="132" s="9" customFormat="1" ht="15" spans="10:10">
+      <c r="J132" s="10"/>
+    </row>
+    <row r="133" s="9" customFormat="1" ht="15" spans="10:10">
+      <c r="J133" s="10"/>
+    </row>
+    <row r="134" s="9" customFormat="1" ht="15" spans="10:10">
+      <c r="J134" s="10"/>
+    </row>
+    <row r="135" s="9" customFormat="1" ht="15" spans="10:10">
+      <c r="J135" s="10"/>
+    </row>
+    <row r="136" s="9" customFormat="1" ht="15" spans="10:10">
+      <c r="J136" s="10"/>
+    </row>
+    <row r="137" s="9" customFormat="1" ht="15" spans="10:10">
+      <c r="J137" s="10"/>
+    </row>
+    <row r="138" s="9" customFormat="1" ht="15" spans="10:10">
+      <c r="J138" s="10"/>
+    </row>
+    <row r="139" s="9" customFormat="1" ht="15" spans="10:10">
+      <c r="J139" s="10"/>
+    </row>
+    <row r="140" s="9" customFormat="1" ht="15" spans="10:10">
+      <c r="J140" s="10"/>
+    </row>
+    <row r="141" s="9" customFormat="1" ht="15" spans="10:10">
+      <c r="J141" s="10"/>
+    </row>
+    <row r="142" s="9" customFormat="1" ht="15" spans="10:10">
+      <c r="J142" s="10"/>
+    </row>
+    <row r="143" s="9" customFormat="1" ht="15" spans="10:10">
+      <c r="J143" s="10"/>
+    </row>
+    <row r="144" s="9" customFormat="1" ht="15" spans="10:10">
+      <c r="J144" s="10"/>
+    </row>
+    <row r="145" s="9" customFormat="1" ht="15" spans="10:10">
+      <c r="J145" s="10"/>
+    </row>
+    <row r="146" s="9" customFormat="1" ht="15" spans="10:10">
+      <c r="J146" s="10"/>
+    </row>
+    <row r="147" s="9" customFormat="1" ht="15" spans="10:10">
+      <c r="J147" s="10"/>
+    </row>
+    <row r="148" s="9" customFormat="1" ht="15" spans="10:10">
+      <c r="J148" s="10"/>
+    </row>
+    <row r="149" s="9" customFormat="1" ht="15" spans="10:10">
+      <c r="J149" s="10"/>
+    </row>
+    <row r="150" s="9" customFormat="1" ht="15" spans="10:10">
+      <c r="J150" s="10"/>
+    </row>
+    <row r="151" s="9" customFormat="1" ht="15" spans="10:10">
+      <c r="J151" s="10"/>
+    </row>
+    <row r="152" s="9" customFormat="1" ht="15" spans="10:10">
+      <c r="J152" s="10"/>
+    </row>
+    <row r="153" s="9" customFormat="1" ht="15" spans="10:10">
+      <c r="J153" s="10"/>
+    </row>
+    <row r="154" s="9" customFormat="1" ht="15" spans="10:10">
+      <c r="J154" s="10"/>
+    </row>
+    <row r="155" s="9" customFormat="1" ht="15" spans="10:10">
+      <c r="J155" s="10"/>
+    </row>
+    <row r="156" s="9" customFormat="1" ht="15" spans="10:10">
+      <c r="J156" s="10"/>
+    </row>
+    <row r="157" s="9" customFormat="1" ht="15" spans="10:10">
+      <c r="J157" s="10"/>
+    </row>
+    <row r="158" s="9" customFormat="1" ht="15" spans="10:10">
+      <c r="J158" s="10"/>
+    </row>
+    <row r="159" s="9" customFormat="1" ht="15" spans="10:10">
+      <c r="J159" s="10"/>
+    </row>
+    <row r="160" s="9" customFormat="1" ht="15" spans="10:10">
+      <c r="J160" s="10"/>
+    </row>
+    <row r="161" s="9" customFormat="1" ht="15" spans="10:10">
+      <c r="J161" s="10"/>
+    </row>
+    <row r="162" s="9" customFormat="1" ht="15" spans="10:10">
+      <c r="J162" s="10"/>
+    </row>
+    <row r="163" s="9" customFormat="1" ht="15" spans="10:10">
+      <c r="J163" s="10"/>
+    </row>
+    <row r="164" s="9" customFormat="1" ht="15" spans="10:10">
+      <c r="J164" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5359,24 +5373,23 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L44"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
+  <dimension ref="A1:J43"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="5.57142857142857" customWidth="1"/>
-    <col min="2" max="2" width="6.28571428571429" customWidth="1"/>
-    <col min="3" max="3" width="9.14285714285714" customWidth="1"/>
-    <col min="4" max="4" width="4.28571428571429" customWidth="1"/>
-    <col min="5" max="5" width="7.28571428571429" customWidth="1"/>
-    <col min="6" max="6" width="6.42857142857143" customWidth="1"/>
-    <col min="7" max="7" width="7.28571428571429" customWidth="1"/>
-    <col min="8" max="8" width="17.2857142857143" customWidth="1"/>
-    <col min="9" max="9" width="26.4285714285714" customWidth="1"/>
-    <col min="10" max="10" width="29.7142857142857" customWidth="1"/>
-    <col min="11" max="11" width="40.2857142857143" customWidth="1"/>
-    <col min="12" max="12" width="37.7142857142857" customWidth="1"/>
+    <col min="1" max="1" width="5.57142857142857" style="5" customWidth="1"/>
+    <col min="2" max="2" width="6.28571428571429" style="5" customWidth="1"/>
+    <col min="3" max="3" width="12.2857142857143" style="5" customWidth="1"/>
+    <col min="4" max="4" width="4.28571428571429" style="5" customWidth="1"/>
+    <col min="5" max="5" width="7.28571428571429" style="5" customWidth="1"/>
+    <col min="6" max="6" width="6.42857142857143" style="5" customWidth="1"/>
+    <col min="7" max="7" width="7.28571428571429" style="5" customWidth="1"/>
+    <col min="8" max="8" width="17.2857142857143" style="5" customWidth="1"/>
+    <col min="9" max="9" width="20.1428571428571" style="5" customWidth="1"/>
+    <col min="10" max="10" width="40.2857142857143" style="5" customWidth="1"/>
+    <col min="11" max="16384" width="9.14285714285714" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="12.75" spans="1:12">
+    <row r="1" s="1" customFormat="1" spans="1:10">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -5402,1029 +5415,946 @@
         <v>7</v>
       </c>
       <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="25.5" spans="1:10">
+      <c r="A2" s="6" t="s">
         <v>239</v>
       </c>
-      <c r="J1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="2" t="s">
+      <c r="B2" s="6" t="s">
         <v>240</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="C2" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="8" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="2" s="1" customFormat="1" ht="51" spans="1:12">
-      <c r="A2" s="1" t="s">
+      <c r="J2" s="8" t="s">
         <v>242</v>
       </c>
-      <c r="B2" s="1" t="s">
+    </row>
+    <row r="3" s="1" customFormat="1" ht="25.5" spans="1:10">
+      <c r="A3" s="6" t="s">
         <v>243</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" s="1" t="s">
+      <c r="B3" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="6" t="s">
         <v>244</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="I3" s="8" t="s">
         <v>245</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="J3" s="8" t="s">
         <v>246</v>
       </c>
-      <c r="L2" s="4" t="s">
+    </row>
+    <row r="4" s="1" customFormat="1" ht="25.5" spans="1:10">
+      <c r="A4" s="6" t="s">
         <v>247</v>
       </c>
-    </row>
-    <row r="3" s="1" customFormat="1" ht="51" spans="1:12">
-      <c r="A3" s="1" t="s">
+      <c r="B4" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="8" t="s">
         <v>248</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H3" s="1" t="s">
+      <c r="J4" s="8" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:10">
+      <c r="A5" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="B5" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:10">
+      <c r="A6" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="6" t="s">
         <v>244</v>
       </c>
-      <c r="J3" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="K3" s="4" t="s">
+      <c r="I6" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="J6" s="8" t="s">
         <v>246</v>
       </c>
-      <c r="L3" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" ht="51" spans="1:12">
-      <c r="A4" s="1" t="s">
-        <v>251</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="K4" s="4" t="s">
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:10">
+      <c r="A7" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="J7" s="8" t="s">
         <v>246</v>
       </c>
-      <c r="L4" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="5" s="1" customFormat="1" ht="51" spans="1:12">
-      <c r="A5" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>255</v>
-      </c>
-      <c r="K5" s="4" t="s">
+    </row>
+    <row r="8" s="1" customFormat="1" ht="25.5" spans="1:10">
+      <c r="A8" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="25.5" spans="1:10">
+      <c r="A9" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="C9" s="6"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" ht="25.5" spans="1:10">
+      <c r="A10" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="C10" s="6"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" ht="25.5" spans="1:10">
+      <c r="A11" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" spans="1:10">
+      <c r="A12" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" ht="25.5" spans="1:10">
+      <c r="A13" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="J13" s="8" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" ht="25.5" spans="1:10">
+      <c r="A14" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="J14" s="8" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" ht="25.5" spans="1:10">
+      <c r="A15" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="I15" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="J15" s="8" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" ht="25.5" spans="1:10">
+      <c r="A16" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="J16" s="8" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" ht="25.5" spans="1:10">
+      <c r="A17" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="J17" s="8" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" ht="25.5" spans="1:10">
+      <c r="A18" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="I18" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="J18" s="8" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" ht="25.5" spans="1:10">
+      <c r="A19" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="6">
+        <v>1062026</v>
+      </c>
+      <c r="I19" s="8" t="s">
+        <v>281</v>
+      </c>
+      <c r="J19" s="8" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" ht="25.5" spans="1:10">
+      <c r="A20" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="7"/>
+      <c r="I20" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="J20" s="8" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" spans="1:10">
+      <c r="A21" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
+      <c r="H21" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="I21" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="J21" s="8" t="s">
         <v>246</v>
       </c>
-      <c r="L5" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" ht="51" spans="1:12">
-      <c r="A6" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="K6" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L6" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" ht="51" spans="1:12">
-      <c r="A7" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="K7" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L7" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" ht="51" spans="1:12">
-      <c r="A8" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="K8" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L8" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" ht="51" spans="1:12">
-      <c r="A9" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="C9" s="3"/>
-      <c r="I9" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="K9" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L9" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" ht="51" spans="1:12">
-      <c r="A10" s="1" t="s">
-        <v>264</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="C10" s="3"/>
-      <c r="I10" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="K10" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L10" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" ht="51" spans="1:12">
-      <c r="A11" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="K11" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L11" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" ht="51" spans="1:12">
-      <c r="A12" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="J12" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="K12" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L12" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="13" s="1" customFormat="1" ht="51" spans="1:12">
-      <c r="A13" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="K13" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L13" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="14" s="1" customFormat="1" ht="51" spans="1:12">
-      <c r="A14" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="J14" s="4" t="s">
-        <v>270</v>
-      </c>
-      <c r="K14" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L14" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="15" s="1" customFormat="1" ht="51" spans="1:12">
-      <c r="A15" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="J15" s="4" t="s">
-        <v>272</v>
-      </c>
-      <c r="K15" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L15" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="16" s="1" customFormat="1" ht="51" spans="1:12">
-      <c r="A16" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H16" s="3"/>
-      <c r="I16" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="J16" s="4" t="s">
-        <v>274</v>
-      </c>
-      <c r="K16" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L16" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="17" s="1" customFormat="1" ht="51" spans="1:12">
-      <c r="A17" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="J17" s="4" t="s">
-        <v>276</v>
-      </c>
-      <c r="K17" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L17" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="18" s="1" customFormat="1" ht="51" spans="1:12">
-      <c r="A18" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="J18" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="K18" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L18" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="19" s="1" customFormat="1" ht="51" spans="1:12">
-      <c r="A19" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H19" s="1">
-        <v>1062026</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="J19" s="4" t="s">
-        <v>281</v>
-      </c>
-      <c r="K19" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L19" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="20" s="1" customFormat="1" ht="51" spans="1:12">
-      <c r="A20" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="J20" s="4" t="s">
-        <v>283</v>
-      </c>
-      <c r="K20" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L20" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="21" s="1" customFormat="1" ht="51" spans="1:12">
-      <c r="A21" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="J21" s="4" t="s">
-        <v>286</v>
-      </c>
-      <c r="K21" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L21" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="22" s="1" customFormat="1" ht="38.25" spans="1:12">
-      <c r="A22" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I22" s="1" t="s">
+    </row>
+    <row r="22" s="1" customFormat="1" ht="25.5" spans="1:10">
+      <c r="A22" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="J22" s="4" t="s">
+      <c r="B22" s="7"/>
+      <c r="C22" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="7"/>
+      <c r="H22" s="7"/>
+      <c r="I22" s="8" t="s">
         <v>289</v>
       </c>
-      <c r="K22" s="4" t="s">
+      <c r="J22" s="8" t="s">
         <v>290</v>
       </c>
-      <c r="L22" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="23" s="1" customFormat="1" ht="12.75" spans="1:12">
-      <c r="A23" s="1" t="s">
+    </row>
+    <row r="23" s="1" customFormat="1" ht="38.25" spans="1:10">
+      <c r="A23" s="6" t="s">
         <v>291</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="C23" s="6" t="s">
         <v>292</v>
       </c>
-      <c r="C23" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I23" s="1" t="s">
+      <c r="D23" s="7"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
+      <c r="H23" s="7"/>
+      <c r="I23" s="8" t="s">
         <v>293</v>
       </c>
-      <c r="J23" s="4" t="s">
+      <c r="J23" s="8" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" ht="25.5" spans="1:10">
+      <c r="A24" s="6" t="s">
         <v>294</v>
       </c>
-      <c r="K23" s="4" t="s">
+      <c r="B24" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7"/>
+      <c r="H24" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="L23" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="24" s="1" customFormat="1" ht="51" spans="1:12">
-      <c r="A24" s="1" t="s">
+      <c r="I24" s="8" t="s">
         <v>296</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="C24" s="1" t="s">
+      <c r="J24" s="8" t="s">
         <v>297</v>
       </c>
-      <c r="I24" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="J24" s="4" t="s">
+    </row>
+    <row r="25" s="1" customFormat="1" ht="25.5" spans="1:10">
+      <c r="A25" s="6" t="s">
         <v>298</v>
       </c>
-      <c r="K24" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L24" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="25" s="1" customFormat="1" ht="51" spans="1:12">
-      <c r="A25" s="1" t="s">
+      <c r="B25" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="C25" s="6" t="s">
         <v>299</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H25" s="1" t="s">
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
+      <c r="H25" s="7"/>
+      <c r="I25" s="8" t="s">
         <v>300</v>
       </c>
-      <c r="I25" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="J25" s="4" t="s">
+      <c r="J25" s="8"/>
+    </row>
+    <row r="26" s="1" customFormat="1" ht="25.5" spans="1:10">
+      <c r="A26" s="6" t="s">
         <v>301</v>
       </c>
-      <c r="K25" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L25" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="26" s="1" customFormat="1" ht="51" spans="1:12">
-      <c r="A26" s="1" t="s">
+      <c r="B26" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="7"/>
+      <c r="H26" s="7"/>
+      <c r="I26" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="J26" s="8" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1" ht="25.5" spans="1:10">
+      <c r="A27" s="6" t="s">
         <v>302</v>
       </c>
-      <c r="B26" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="C26" s="1" t="s">
+      <c r="B27" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="7"/>
+      <c r="G27" s="7"/>
+      <c r="H27" s="7"/>
+      <c r="I27" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="J27" s="8" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="28" s="1" customFormat="1" ht="25.5" spans="1:10">
+      <c r="A28" s="6" t="s">
         <v>303</v>
       </c>
-      <c r="I26" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="J26" s="4" t="s">
+      <c r="B28" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="7"/>
+      <c r="H28" s="7"/>
+      <c r="I28" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="J28" s="8" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="29" s="1" customFormat="1" ht="25.5" spans="1:10">
+      <c r="A29" s="6" t="s">
         <v>304</v>
       </c>
-      <c r="K26" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L26" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="27" s="1" customFormat="1" ht="51" spans="1:12">
-      <c r="A27" s="1" t="s">
+      <c r="B29" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="7"/>
+      <c r="G29" s="7"/>
+      <c r="H29" s="7"/>
+      <c r="I29" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="J29" s="8" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="30" s="1" customFormat="1" ht="25.5" spans="1:10">
+      <c r="A30" s="6" t="s">
         <v>305</v>
       </c>
-      <c r="B27" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="J27" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="K27" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L27" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="28" s="1" customFormat="1" ht="51" spans="1:12">
-      <c r="A28" s="1" t="s">
+      <c r="B30" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
+      <c r="F30" s="7"/>
+      <c r="G30" s="7"/>
+      <c r="H30" s="7"/>
+      <c r="I30" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="J30" s="8" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="31" s="1" customFormat="1" ht="25.5" spans="1:10">
+      <c r="A31" s="6" t="s">
         <v>306</v>
       </c>
-      <c r="B28" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I28" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="J28" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="K28" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L28" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="29" s="1" customFormat="1" ht="51" spans="1:12">
-      <c r="A29" s="1" t="s">
+      <c r="B31" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="D31" s="7"/>
+      <c r="E31" s="7"/>
+      <c r="F31" s="7"/>
+      <c r="G31" s="7"/>
+      <c r="H31" s="7"/>
+      <c r="I31" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="J31" s="8" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="32" s="1" customFormat="1" ht="25.5" spans="1:10">
+      <c r="A32" s="6" t="s">
         <v>307</v>
       </c>
-      <c r="B29" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I29" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="J29" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="K29" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L29" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="30" s="1" customFormat="1" ht="51" spans="1:12">
-      <c r="A30" s="1" t="s">
+      <c r="B32" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D32" s="7"/>
+      <c r="E32" s="7"/>
+      <c r="F32" s="7"/>
+      <c r="G32" s="7"/>
+      <c r="H32" s="7"/>
+      <c r="I32" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="J32" s="8" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="33" s="1" customFormat="1" ht="25.5" spans="1:10">
+      <c r="A33" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="B30" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="I30" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="J30" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="K30" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L30" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="31" s="1" customFormat="1" ht="51" spans="1:12">
-      <c r="A31" s="1" t="s">
+      <c r="B33" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="7"/>
+      <c r="G33" s="7"/>
+      <c r="H33" s="7"/>
+      <c r="I33" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="J33" s="8" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="34" s="1" customFormat="1" ht="25.5" spans="1:10">
+      <c r="A34" s="6" t="s">
         <v>309</v>
       </c>
-      <c r="B31" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="I31" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="J31" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="K31" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L31" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="32" s="1" customFormat="1" ht="51" spans="1:12">
-      <c r="A32" s="1" t="s">
+      <c r="B34" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D34" s="7"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="7"/>
+      <c r="G34" s="7"/>
+      <c r="H34" s="7"/>
+      <c r="I34" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="J34" s="8" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="35" s="1" customFormat="1" ht="25.5" spans="1:10">
+      <c r="A35" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="B32" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="I32" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="J32" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="K32" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L32" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="33" s="1" customFormat="1" ht="51" spans="1:12">
-      <c r="A33" s="1" t="s">
+      <c r="B35" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D35" s="7"/>
+      <c r="E35" s="7"/>
+      <c r="F35" s="7"/>
+      <c r="G35" s="7"/>
+      <c r="H35" s="7"/>
+      <c r="I35" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="J35" s="8" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="36" s="1" customFormat="1" ht="25.5" spans="1:10">
+      <c r="A36" s="6" t="s">
         <v>311</v>
       </c>
-      <c r="B33" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I33" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="J33" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="K33" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L33" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="34" s="1" customFormat="1" ht="51" spans="1:12">
-      <c r="A34" s="1" t="s">
+      <c r="B36" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D36" s="7"/>
+      <c r="E36" s="7"/>
+      <c r="F36" s="7"/>
+      <c r="G36" s="7"/>
+      <c r="H36" s="7"/>
+      <c r="I36" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="J36" s="8" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="37" s="1" customFormat="1" ht="25.5" spans="1:10">
+      <c r="A37" s="6" t="s">
         <v>312</v>
       </c>
-      <c r="B34" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I34" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="J34" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="K34" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L34" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="35" s="1" customFormat="1" ht="51" spans="1:12">
-      <c r="A35" s="1" t="s">
+      <c r="B37" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D37" s="7"/>
+      <c r="E37" s="7"/>
+      <c r="F37" s="7"/>
+      <c r="G37" s="7"/>
+      <c r="H37" s="7"/>
+      <c r="I37" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="J37" s="8" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="38" s="1" customFormat="1" ht="25.5" spans="1:10">
+      <c r="A38" s="6" t="s">
         <v>313</v>
       </c>
-      <c r="B35" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="C35" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I35" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="J35" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="K35" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L35" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="36" s="1" customFormat="1" ht="51" spans="1:12">
-      <c r="A36" s="1" t="s">
+      <c r="B38" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D38" s="7"/>
+      <c r="E38" s="7"/>
+      <c r="F38" s="7"/>
+      <c r="G38" s="7"/>
+      <c r="H38" s="7"/>
+      <c r="I38" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="J38" s="8" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="39" s="1" customFormat="1" ht="25.5" spans="1:10">
+      <c r="A39" s="6" t="s">
         <v>314</v>
       </c>
-      <c r="B36" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I36" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="J36" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="K36" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L36" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="37" s="1" customFormat="1" ht="51" spans="1:12">
-      <c r="A37" s="1" t="s">
+      <c r="B39" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D39" s="7"/>
+      <c r="E39" s="7"/>
+      <c r="F39" s="7"/>
+      <c r="G39" s="7"/>
+      <c r="H39" s="7"/>
+      <c r="I39" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="J39" s="8" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="40" s="1" customFormat="1" ht="25.5" spans="1:10">
+      <c r="A40" s="6" t="s">
         <v>315</v>
       </c>
-      <c r="B37" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I37" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="J37" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="K37" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L37" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="38" s="1" customFormat="1" ht="51" spans="1:12">
-      <c r="A38" s="1" t="s">
+      <c r="B40" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D40" s="7"/>
+      <c r="E40" s="7"/>
+      <c r="F40" s="7"/>
+      <c r="G40" s="7"/>
+      <c r="H40" s="7"/>
+      <c r="I40" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="J40" s="8" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="41" s="1" customFormat="1" ht="25.5" spans="1:10">
+      <c r="A41" s="6" t="s">
         <v>316</v>
       </c>
-      <c r="B38" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I38" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="J38" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="K38" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L38" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="39" s="1" customFormat="1" ht="51" spans="1:12">
-      <c r="A39" s="1" t="s">
+      <c r="B41" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D41" s="7"/>
+      <c r="E41" s="7"/>
+      <c r="F41" s="7"/>
+      <c r="G41" s="7"/>
+      <c r="H41" s="7"/>
+      <c r="I41" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="J41" s="8" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="42" s="1" customFormat="1" ht="25.5" spans="1:10">
+      <c r="A42" s="6" t="s">
         <v>317</v>
       </c>
-      <c r="B39" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I39" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="J39" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="K39" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L39" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="40" s="1" customFormat="1" ht="51" spans="1:12">
-      <c r="A40" s="1" t="s">
+      <c r="B42" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D42" s="7"/>
+      <c r="E42" s="7"/>
+      <c r="F42" s="7"/>
+      <c r="G42" s="7"/>
+      <c r="H42" s="7"/>
+      <c r="I42" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="J42" s="8" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="43" s="1" customFormat="1" ht="25.5" spans="1:10">
+      <c r="A43" s="6" t="s">
         <v>318</v>
       </c>
-      <c r="B40" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I40" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="J40" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="K40" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L40" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="41" s="1" customFormat="1" ht="51" spans="1:12">
-      <c r="A41" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I41" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="J41" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="K41" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L41" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="42" s="1" customFormat="1" ht="51" spans="1:12">
-      <c r="A42" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I42" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="J42" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="K42" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L42" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="43" s="1" customFormat="1" ht="51" spans="1:12">
-      <c r="A43" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I43" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="J43" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="K43" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L43" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="44" s="1" customFormat="1" ht="51" spans="1:12">
-      <c r="A44" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="I44" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="J44" s="4" t="s">
+      <c r="B43" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D43" s="7"/>
+      <c r="E43" s="7"/>
+      <c r="F43" s="7"/>
+      <c r="G43" s="7"/>
+      <c r="H43" s="7"/>
+      <c r="I43" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="K44" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L44" s="4" t="s">
-        <v>247</v>
+      <c r="J43" s="8" t="s">
+        <v>242</v>
       </c>
     </row>
   </sheetData>
@@ -6436,7 +6366,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L66"/>
+  <dimension ref="A1:J66"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.57142857142857" customWidth="1"/>
@@ -6446,13 +6376,11 @@
     <col min="5" max="6" width="8.28571428571429" customWidth="1"/>
     <col min="7" max="7" width="7.28571428571429" customWidth="1"/>
     <col min="8" max="8" width="5.14285714285714" customWidth="1"/>
-    <col min="9" max="9" width="18.8571428571429" customWidth="1"/>
-    <col min="10" max="10" width="28.8571428571429" customWidth="1"/>
-    <col min="11" max="11" width="35" customWidth="1"/>
-    <col min="12" max="12" width="37.7142857142857" customWidth="1"/>
+    <col min="9" max="9" width="28.8571428571429" customWidth="1"/>
+    <col min="10" max="10" width="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="25.5" spans="1:12">
+    <row r="1" s="1" customFormat="1" ht="25.5" spans="1:10">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -6478,24 +6406,18 @@
         <v>7</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>239</v>
+        <v>8</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="2" s="1" customFormat="1" ht="63.75" spans="1:12">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" ht="63.75" spans="1:10">
       <c r="A2" s="1" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>12</v>
@@ -6509,25 +6431,19 @@
       <c r="F2" s="1">
         <v>5</v>
       </c>
-      <c r="I2" s="1" t="s">
-        <v>244</v>
+      <c r="I2" s="4" t="s">
+        <v>321</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>325</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" ht="63.75" spans="1:12">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="63.75" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>12</v>
@@ -6541,25 +6457,19 @@
       <c r="F3" s="1">
         <v>0</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>244</v>
+      <c r="I3" s="4" t="s">
+        <v>324</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>327</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L3" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="4" s="1" customFormat="1" ht="63.75" spans="1:12">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" ht="63.75" spans="1:10">
       <c r="A4" s="1" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>12</v>
@@ -6573,25 +6483,19 @@
       <c r="F4" s="1">
         <v>127</v>
       </c>
-      <c r="I4" s="1" t="s">
-        <v>244</v>
+      <c r="I4" s="4" t="s">
+        <v>326</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>329</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L4" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="5" s="1" customFormat="1" ht="63.75" spans="1:12">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="63.75" spans="1:10">
       <c r="A5" s="1" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>12</v>
@@ -6605,28 +6509,22 @@
       <c r="F5" s="1">
         <v>5</v>
       </c>
-      <c r="I5" s="1" t="s">
-        <v>244</v>
+      <c r="I5" s="4" t="s">
+        <v>328</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>331</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" ht="63.75" spans="1:12">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" ht="63.75" spans="1:10">
       <c r="A6" s="1" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="D6" s="1">
         <v>15072026</v>
@@ -6637,25 +6535,19 @@
       <c r="F6" s="1">
         <v>5</v>
       </c>
-      <c r="I6" s="1" t="s">
-        <v>244</v>
+      <c r="I6" s="4" t="s">
+        <v>330</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>333</v>
-      </c>
-      <c r="K6" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L6" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" ht="63.75" spans="1:12">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="63.75" spans="1:10">
       <c r="A7" s="1" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="1">
@@ -6667,25 +6559,19 @@
       <c r="F7" s="1">
         <v>5</v>
       </c>
-      <c r="I7" s="1" t="s">
-        <v>244</v>
+      <c r="I7" s="4" t="s">
+        <v>52</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="K7" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L7" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" ht="63.75" spans="1:12">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" ht="63.75" spans="1:10">
       <c r="A8" s="1" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C8" s="3"/>
       <c r="D8" s="1">
@@ -6697,25 +6583,19 @@
       <c r="F8" s="1">
         <v>5</v>
       </c>
-      <c r="I8" s="1" t="s">
-        <v>244</v>
+      <c r="I8" s="4" t="s">
+        <v>55</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="K8" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L8" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" ht="63.75" spans="1:12">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="63.75" spans="1:10">
       <c r="A9" s="1" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>198</v>
@@ -6729,25 +6609,19 @@
       <c r="F9" s="1">
         <v>5</v>
       </c>
-      <c r="I9" s="1" t="s">
-        <v>244</v>
+      <c r="I9" s="4" t="s">
+        <v>58</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="K9" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L9" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" ht="63.75" spans="1:12">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" ht="63.75" spans="1:10">
       <c r="A10" s="1" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>61</v>
@@ -6761,25 +6635,19 @@
       <c r="F10" s="1">
         <v>5</v>
       </c>
-      <c r="I10" s="1" t="s">
-        <v>244</v>
+      <c r="I10" s="4" t="s">
+        <v>62</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="K10" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L10" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" ht="63.75" spans="1:12">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" ht="63.75" spans="1:10">
       <c r="A11" s="1" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>65</v>
@@ -6793,25 +6661,19 @@
       <c r="F11" s="1">
         <v>5</v>
       </c>
-      <c r="I11" s="1" t="s">
-        <v>244</v>
+      <c r="I11" s="4" t="s">
+        <v>66</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="K11" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L11" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" ht="63.75" spans="1:12">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" ht="63.75" spans="1:10">
       <c r="A12" s="1" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>12</v>
@@ -6825,25 +6687,19 @@
       <c r="F12" s="1">
         <v>5</v>
       </c>
-      <c r="I12" s="1" t="s">
-        <v>244</v>
+      <c r="I12" s="4" t="s">
+        <v>337</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>340</v>
-      </c>
-      <c r="K12" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L12" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="13" s="1" customFormat="1" ht="63.75" spans="1:12">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" ht="63.75" spans="1:10">
       <c r="A13" s="1" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>12</v>
@@ -6857,25 +6713,19 @@
       <c r="F13" s="1">
         <v>5</v>
       </c>
-      <c r="I13" s="1" t="s">
-        <v>244</v>
+      <c r="I13" s="4" t="s">
+        <v>339</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>342</v>
-      </c>
-      <c r="K13" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L13" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="14" s="1" customFormat="1" ht="63.75" spans="1:12">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" ht="63.75" spans="1:10">
       <c r="A14" s="1" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>12</v>
@@ -6886,25 +6736,19 @@
       <c r="F14" s="1">
         <v>5</v>
       </c>
-      <c r="I14" s="1" t="s">
-        <v>244</v>
+      <c r="I14" s="4" t="s">
+        <v>75</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="K14" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L14" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="15" s="1" customFormat="1" ht="63.75" spans="1:12">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" ht="63.75" spans="1:10">
       <c r="A15" s="1" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>12</v>
@@ -6915,25 +6759,19 @@
       <c r="F15" s="1">
         <v>5</v>
       </c>
-      <c r="I15" s="1" t="s">
-        <v>244</v>
+      <c r="I15" s="4" t="s">
+        <v>342</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>345</v>
-      </c>
-      <c r="K15" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L15" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="16" s="1" customFormat="1" ht="63.75" spans="1:12">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" ht="63.75" spans="1:10">
       <c r="A16" s="1" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>12</v>
@@ -6947,25 +6785,19 @@
       <c r="F16" s="1">
         <v>5</v>
       </c>
-      <c r="I16" s="1" t="s">
-        <v>244</v>
+      <c r="I16" s="4" t="s">
+        <v>81</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="K16" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L16" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="17" s="1" customFormat="1" ht="63.75" spans="1:12">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" ht="63.75" spans="1:10">
       <c r="A17" s="1" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>12</v>
@@ -6979,25 +6811,19 @@
       <c r="F17" s="1">
         <v>5</v>
       </c>
-      <c r="I17" s="1" t="s">
-        <v>244</v>
+      <c r="I17" s="4" t="s">
+        <v>78</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="K17" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L17" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="18" s="1" customFormat="1" ht="63.75" spans="1:12">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" ht="63.75" spans="1:10">
       <c r="A18" s="1" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>12</v>
@@ -7011,31 +6837,25 @@
       <c r="F18" s="1">
         <v>5</v>
       </c>
-      <c r="I18" s="1" t="s">
-        <v>244</v>
+      <c r="I18" s="4" t="s">
+        <v>346</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>349</v>
-      </c>
-      <c r="K18" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L18" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="19" s="1" customFormat="1" ht="63.75" spans="1:12">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" ht="63.75" spans="1:10">
       <c r="A19" s="1" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="E19" s="1">
         <v>10</v>
@@ -7043,25 +6863,19 @@
       <c r="F19" s="1">
         <v>5</v>
       </c>
-      <c r="I19" s="1" t="s">
-        <v>244</v>
+      <c r="I19" s="4" t="s">
+        <v>349</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>352</v>
-      </c>
-      <c r="K19" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L19" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="20" s="1" customFormat="1" ht="63.75" spans="1:12">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" ht="63.75" spans="1:10">
       <c r="A20" s="1" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>12</v>
@@ -7075,31 +6889,25 @@
       <c r="F20" s="1">
         <v>5</v>
       </c>
-      <c r="I20" s="1" t="s">
-        <v>244</v>
+      <c r="I20" s="4" t="s">
+        <v>351</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>354</v>
-      </c>
-      <c r="K20" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L20" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="21" s="1" customFormat="1" ht="63.75" spans="1:12">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" ht="63.75" spans="1:10">
       <c r="A21" s="1" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="E21" s="1">
         <v>10</v>
@@ -7107,25 +6915,19 @@
       <c r="F21" s="1">
         <v>5</v>
       </c>
-      <c r="I21" s="1" t="s">
-        <v>244</v>
+      <c r="I21" s="4" t="s">
+        <v>73</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="K21" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L21" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="22" s="1" customFormat="1" ht="63.75" spans="1:12">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="22" s="1" customFormat="1" ht="63.75" spans="1:10">
       <c r="A22" s="1" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>12</v>
@@ -7136,25 +6938,19 @@
       <c r="F22" s="1">
         <v>5</v>
       </c>
-      <c r="I22" s="1" t="s">
-        <v>244</v>
+      <c r="I22" s="4" t="s">
+        <v>98</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="K22" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L22" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="23" s="1" customFormat="1" ht="63.75" spans="1:12">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="23" s="1" customFormat="1" ht="63.75" spans="1:10">
       <c r="A23" s="1" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>12</v>
@@ -7165,25 +6961,19 @@
       <c r="F23" s="1">
         <v>5</v>
       </c>
-      <c r="I23" s="1" t="s">
-        <v>244</v>
+      <c r="I23" s="4" t="s">
+        <v>101</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="K23" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L23" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="24" s="1" customFormat="1" ht="63.75" spans="1:12">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" ht="63.75" spans="1:10">
       <c r="A24" s="1" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>12</v>
@@ -7197,25 +6987,19 @@
       <c r="F24" s="1">
         <v>5</v>
       </c>
-      <c r="I24" s="1" t="s">
-        <v>244</v>
+      <c r="I24" s="4" t="s">
+        <v>95</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="K24" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L24" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="25" s="1" customFormat="1" ht="63.75" spans="1:12">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="25" s="1" customFormat="1" ht="63.75" spans="1:10">
       <c r="A25" s="1" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>12</v>
@@ -7229,25 +7013,19 @@
       <c r="F25" s="1">
         <v>5</v>
       </c>
-      <c r="I25" s="1" t="s">
-        <v>244</v>
+      <c r="I25" s="4" t="s">
+        <v>104</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="K25" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L25" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="26" s="1" customFormat="1" ht="63.75" spans="1:12">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="1" ht="63.75" spans="1:10">
       <c r="A26" s="1" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>12</v>
@@ -7261,25 +7039,19 @@
       <c r="F26" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="I26" s="1" t="s">
-        <v>244</v>
+      <c r="I26" s="4" t="s">
+        <v>116</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="K26" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L26" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="27" s="1" customFormat="1" ht="63.75" spans="1:12">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1" ht="63.75" spans="1:10">
       <c r="A27" s="1" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>12</v>
@@ -7293,25 +7065,19 @@
       <c r="F27" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="I27" s="1" t="s">
-        <v>244</v>
+      <c r="I27" s="4" t="s">
+        <v>119</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="K27" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L27" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="28" s="1" customFormat="1" ht="63.75" spans="1:12">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="28" s="1" customFormat="1" ht="63.75" spans="1:10">
       <c r="A28" s="1" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>12</v>
@@ -7325,25 +7091,19 @@
       <c r="F28" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="I28" s="1" t="s">
-        <v>244</v>
+      <c r="I28" s="4" t="s">
+        <v>112</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="K28" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L28" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="29" s="1" customFormat="1" ht="63.75" spans="1:12">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="29" s="1" customFormat="1" ht="63.75" spans="1:10">
       <c r="A29" s="1" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>12</v>
@@ -7357,25 +7117,19 @@
       <c r="F29" s="1">
         <v>9999</v>
       </c>
-      <c r="I29" s="1" t="s">
-        <v>244</v>
+      <c r="I29" s="4" t="s">
+        <v>122</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="K29" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L29" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="30" s="1" customFormat="1" ht="63.75" spans="1:12">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="30" s="1" customFormat="1" ht="63.75" spans="1:10">
       <c r="A30" s="1" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>12</v>
@@ -7389,25 +7143,19 @@
       <c r="F30" s="1">
         <v>5</v>
       </c>
-      <c r="I30" s="1" t="s">
-        <v>244</v>
+      <c r="I30" s="4" t="s">
+        <v>363</v>
       </c>
       <c r="J30" s="4" t="s">
-        <v>366</v>
-      </c>
-      <c r="K30" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L30" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="31" s="1" customFormat="1" ht="63.75" spans="1:12">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="31" s="1" customFormat="1" ht="63.75" spans="1:10">
       <c r="A31" s="1" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>12</v>
@@ -7421,25 +7169,19 @@
       <c r="F31" s="1">
         <v>5</v>
       </c>
-      <c r="I31" s="1" t="s">
-        <v>244</v>
+      <c r="I31" s="4" t="s">
+        <v>365</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>368</v>
-      </c>
-      <c r="K31" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L31" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="32" s="1" customFormat="1" ht="63.75" spans="1:12">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="32" s="1" customFormat="1" ht="63.75" spans="1:10">
       <c r="A32" s="1" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>12</v>
@@ -7453,25 +7195,19 @@
       <c r="F32" s="1">
         <v>5</v>
       </c>
-      <c r="I32" s="1" t="s">
-        <v>244</v>
+      <c r="I32" s="4" t="s">
+        <v>110</v>
       </c>
       <c r="J32" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="K32" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L32" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="33" s="1" customFormat="1" ht="63.75" spans="1:12">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="33" s="1" customFormat="1" ht="63.75" spans="1:10">
       <c r="A33" s="1" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>12</v>
@@ -7485,25 +7221,19 @@
       <c r="F33" s="1">
         <v>5</v>
       </c>
-      <c r="I33" s="1" t="s">
-        <v>244</v>
+      <c r="I33" s="4" t="s">
+        <v>368</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>371</v>
-      </c>
-      <c r="K33" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L33" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="34" s="1" customFormat="1" ht="25.5" spans="1:12">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="34" s="1" customFormat="1" ht="25.5" spans="1:10">
       <c r="A34" s="1" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>292</v>
+        <v>370</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>12</v>
@@ -7517,28 +7247,22 @@
       <c r="F34" s="1">
         <v>5</v>
       </c>
-      <c r="I34" s="1" t="s">
-        <v>244</v>
+      <c r="I34" s="4" t="s">
+        <v>371</v>
       </c>
       <c r="J34" s="4" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="35" s="1" customFormat="1" ht="63.75" spans="1:10">
+      <c r="A35" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="K34" s="4" t="s">
-        <v>374</v>
-      </c>
-      <c r="L34" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="35" s="1" customFormat="1" ht="63.75" spans="1:12">
-      <c r="A35" s="1" t="s">
-        <v>375</v>
-      </c>
       <c r="B35" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="D35" s="1">
         <v>15072026</v>
@@ -7549,25 +7273,19 @@
       <c r="F35" s="1">
         <v>5</v>
       </c>
-      <c r="I35" s="1" t="s">
-        <v>244</v>
+      <c r="I35" s="4" t="s">
+        <v>374</v>
       </c>
       <c r="J35" s="4" t="s">
-        <v>376</v>
-      </c>
-      <c r="K35" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L35" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="36" s="1" customFormat="1" ht="63.75" spans="1:12">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="36" s="1" customFormat="1" ht="63.75" spans="1:10">
       <c r="A36" s="1" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>12</v>
@@ -7581,25 +7299,19 @@
       <c r="F36" s="1">
         <v>0</v>
       </c>
-      <c r="I36" s="1" t="s">
-        <v>244</v>
+      <c r="I36" s="4" t="s">
+        <v>376</v>
       </c>
       <c r="J36" s="4" t="s">
-        <v>378</v>
-      </c>
-      <c r="K36" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L36" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="37" s="1" customFormat="1" ht="63.75" spans="1:12">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="37" s="1" customFormat="1" ht="63.75" spans="1:10">
       <c r="A37" s="1" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>12</v>
@@ -7613,25 +7325,19 @@
       <c r="F37" s="1">
         <v>1</v>
       </c>
-      <c r="I37" s="1" t="s">
-        <v>244</v>
+      <c r="I37" s="4" t="s">
+        <v>378</v>
       </c>
       <c r="J37" s="4" t="s">
-        <v>380</v>
-      </c>
-      <c r="K37" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L37" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="38" s="1" customFormat="1" ht="63.75" spans="1:12">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="38" s="1" customFormat="1" ht="63.75" spans="1:10">
       <c r="A38" s="1" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>12</v>
@@ -7645,25 +7351,19 @@
       <c r="F38" s="1">
         <v>255</v>
       </c>
-      <c r="I38" s="1" t="s">
-        <v>244</v>
+      <c r="I38" s="4" t="s">
+        <v>380</v>
       </c>
       <c r="J38" s="4" t="s">
-        <v>382</v>
-      </c>
-      <c r="K38" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L38" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="39" s="1" customFormat="1" ht="63.75" spans="1:12">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="39" s="1" customFormat="1" ht="63.75" spans="1:10">
       <c r="A39" s="1" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>12</v>
@@ -7677,25 +7377,19 @@
       <c r="F39" s="1">
         <v>256</v>
       </c>
-      <c r="I39" s="1" t="s">
-        <v>244</v>
+      <c r="I39" s="4" t="s">
+        <v>382</v>
       </c>
       <c r="J39" s="4" t="s">
-        <v>384</v>
-      </c>
-      <c r="K39" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L39" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="40" s="1" customFormat="1" ht="63.75" spans="1:12">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="40" s="1" customFormat="1" ht="63.75" spans="1:10">
       <c r="A40" s="1" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>12</v>
@@ -7709,25 +7403,19 @@
       <c r="F40" s="1">
         <v>5</v>
       </c>
-      <c r="I40" s="1" t="s">
-        <v>244</v>
+      <c r="I40" s="4" t="s">
+        <v>193</v>
       </c>
       <c r="J40" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="K40" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L40" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="41" s="1" customFormat="1" ht="63.75" spans="1:12">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="41" s="1" customFormat="1" ht="63.75" spans="1:10">
       <c r="A41" s="1" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>12</v>
@@ -7741,25 +7429,19 @@
       <c r="F41" s="1">
         <v>5</v>
       </c>
-      <c r="I41" s="1" t="s">
-        <v>244</v>
+      <c r="I41" s="4" t="s">
+        <v>195</v>
       </c>
       <c r="J41" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="K41" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L41" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="42" s="1" customFormat="1" ht="63.75" spans="1:12">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="42" s="1" customFormat="1" ht="63.75" spans="1:10">
       <c r="A42" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>12</v>
@@ -7773,25 +7455,19 @@
       <c r="F42" s="1">
         <v>5</v>
       </c>
-      <c r="I42" s="1" t="s">
-        <v>244</v>
+      <c r="I42" s="4" t="s">
+        <v>167</v>
       </c>
       <c r="J42" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="K42" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L42" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="43" s="1" customFormat="1" ht="63.75" spans="1:12">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="43" s="1" customFormat="1" ht="63.75" spans="1:10">
       <c r="A43" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>65</v>
@@ -7805,25 +7481,19 @@
       <c r="F43" s="1">
         <v>5</v>
       </c>
-      <c r="I43" s="1" t="s">
-        <v>244</v>
+      <c r="I43" s="4" t="s">
+        <v>199</v>
       </c>
       <c r="J43" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="K43" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L43" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="44" s="1" customFormat="1" ht="63.75" spans="1:12">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="44" s="1" customFormat="1" ht="63.75" spans="1:10">
       <c r="A44" s="1" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>68</v>
@@ -7837,25 +7507,19 @@
       <c r="F44" s="1">
         <v>5</v>
       </c>
-      <c r="I44" s="1" t="s">
-        <v>244</v>
+      <c r="I44" s="4" t="s">
+        <v>201</v>
       </c>
       <c r="J44" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="K44" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L44" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="45" s="1" customFormat="1" ht="63.75" spans="1:12">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="45" s="1" customFormat="1" ht="63.75" spans="1:10">
       <c r="A45" s="1" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>203</v>
@@ -7869,25 +7533,19 @@
       <c r="F45" s="1">
         <v>5</v>
       </c>
-      <c r="I45" s="1" t="s">
-        <v>244</v>
+      <c r="I45" s="4" t="s">
+        <v>204</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="K45" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L45" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="46" s="1" customFormat="1" ht="63.75" spans="1:12">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="46" s="1" customFormat="1" ht="63.75" spans="1:10">
       <c r="A46" s="1" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>12</v>
@@ -7901,25 +7559,19 @@
       <c r="F46" s="1">
         <v>5</v>
       </c>
-      <c r="I46" s="1" t="s">
-        <v>244</v>
+      <c r="I46" s="4" t="s">
+        <v>206</v>
       </c>
       <c r="J46" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="K46" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L46" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="47" s="1" customFormat="1" ht="63.75" spans="1:12">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="47" s="1" customFormat="1" ht="63.75" spans="1:10">
       <c r="A47" s="1" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>12</v>
@@ -7933,25 +7585,19 @@
       <c r="F47" s="1">
         <v>5</v>
       </c>
-      <c r="I47" s="1" t="s">
-        <v>244</v>
+      <c r="I47" s="4" t="s">
+        <v>208</v>
       </c>
       <c r="J47" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="K47" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L47" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="48" s="1" customFormat="1" ht="63.75" spans="1:12">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="48" s="1" customFormat="1" ht="63.75" spans="1:10">
       <c r="A48" s="1" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>12</v>
@@ -7965,25 +7611,19 @@
       <c r="F48" s="1">
         <v>5</v>
       </c>
-      <c r="I48" s="1" t="s">
-        <v>244</v>
+      <c r="I48" s="4" t="s">
+        <v>210</v>
       </c>
       <c r="J48" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="K48" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L48" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="49" s="1" customFormat="1" ht="63.75" spans="1:12">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="49" s="1" customFormat="1" ht="63.75" spans="1:10">
       <c r="A49" s="1" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>12</v>
@@ -7997,25 +7637,19 @@
       <c r="F49" s="1">
         <v>5</v>
       </c>
-      <c r="I49" s="1" t="s">
-        <v>244</v>
+      <c r="I49" s="4" t="s">
+        <v>212</v>
       </c>
       <c r="J49" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="K49" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L49" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="50" s="1" customFormat="1" ht="63.75" spans="1:12">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="50" s="1" customFormat="1" ht="63.75" spans="1:10">
       <c r="A50" s="1" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>12</v>
@@ -8029,25 +7663,19 @@
       <c r="F50" s="1">
         <v>5</v>
       </c>
-      <c r="I50" s="1" t="s">
-        <v>244</v>
+      <c r="I50" s="4" t="s">
+        <v>214</v>
       </c>
       <c r="J50" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="K50" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L50" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="51" s="1" customFormat="1" ht="63.75" spans="1:12">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="51" s="1" customFormat="1" ht="63.75" spans="1:10">
       <c r="A51" s="1" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>12</v>
@@ -8061,25 +7689,19 @@
       <c r="F51" s="1">
         <v>5</v>
       </c>
-      <c r="I51" s="1" t="s">
-        <v>244</v>
+      <c r="I51" s="4" t="s">
+        <v>157</v>
       </c>
       <c r="J51" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="K51" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L51" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="52" s="1" customFormat="1" ht="63.75" spans="1:12">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="52" s="1" customFormat="1" ht="63.75" spans="1:10">
       <c r="A52" s="1" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>12</v>
@@ -8093,25 +7715,19 @@
       <c r="F52" s="1">
         <v>5</v>
       </c>
-      <c r="I52" s="1" t="s">
-        <v>244</v>
+      <c r="I52" s="4" t="s">
+        <v>159</v>
       </c>
       <c r="J52" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="K52" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L52" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="53" s="1" customFormat="1" ht="63.75" spans="1:12">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="53" s="1" customFormat="1" ht="63.75" spans="1:10">
       <c r="A53" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>12</v>
@@ -8125,25 +7741,19 @@
       <c r="F53" s="1">
         <v>5</v>
       </c>
-      <c r="I53" s="1" t="s">
-        <v>244</v>
+      <c r="I53" s="4" t="s">
+        <v>161</v>
       </c>
       <c r="J53" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="K53" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L53" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="54" s="1" customFormat="1" ht="63.75" spans="1:12">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="54" s="1" customFormat="1" ht="63.75" spans="1:10">
       <c r="A54" s="1" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>12</v>
@@ -8157,25 +7767,19 @@
       <c r="F54" s="1">
         <v>5</v>
       </c>
-      <c r="I54" s="1" t="s">
-        <v>244</v>
+      <c r="I54" s="4" t="s">
+        <v>163</v>
       </c>
       <c r="J54" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="K54" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L54" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="55" s="1" customFormat="1" ht="63.75" spans="1:12">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="55" s="1" customFormat="1" ht="63.75" spans="1:10">
       <c r="A55" s="1" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>12</v>
@@ -8189,25 +7793,19 @@
       <c r="F55" s="1">
         <v>5</v>
       </c>
-      <c r="I55" s="1" t="s">
-        <v>244</v>
+      <c r="I55" s="4" t="s">
+        <v>165</v>
       </c>
       <c r="J55" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="K55" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L55" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="56" s="1" customFormat="1" ht="63.75" spans="1:12">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="56" s="1" customFormat="1" ht="63.75" spans="1:10">
       <c r="A56" s="1" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>12</v>
@@ -8221,25 +7819,19 @@
       <c r="F56" s="1">
         <v>5</v>
       </c>
-      <c r="I56" s="1" t="s">
-        <v>244</v>
+      <c r="I56" s="4" t="s">
+        <v>222</v>
       </c>
       <c r="J56" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="K56" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L56" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="57" s="1" customFormat="1" ht="63.75" spans="1:12">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="57" s="1" customFormat="1" ht="63.75" spans="1:10">
       <c r="A57" s="1" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>12</v>
@@ -8253,25 +7845,19 @@
       <c r="F57" s="1">
         <v>5</v>
       </c>
-      <c r="I57" s="1" t="s">
-        <v>244</v>
+      <c r="I57" s="4" t="s">
+        <v>224</v>
       </c>
       <c r="J57" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="K57" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L57" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="58" s="1" customFormat="1" ht="63.75" spans="1:12">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="58" s="1" customFormat="1" ht="63.75" spans="1:10">
       <c r="A58" s="1" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>12</v>
@@ -8285,25 +7871,19 @@
       <c r="F58" s="1">
         <v>5</v>
       </c>
-      <c r="I58" s="1" t="s">
-        <v>244</v>
+      <c r="I58" s="4" t="s">
+        <v>402</v>
       </c>
       <c r="J58" s="4" t="s">
-        <v>404</v>
-      </c>
-      <c r="K58" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L58" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="59" s="1" customFormat="1" ht="63.75" spans="1:12">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="59" s="1" customFormat="1" ht="63.75" spans="1:10">
       <c r="A59" s="1" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>12</v>
@@ -8317,25 +7897,19 @@
       <c r="F59" s="1">
         <v>5</v>
       </c>
-      <c r="I59" s="1" t="s">
-        <v>244</v>
+      <c r="I59" s="4" t="s">
+        <v>404</v>
       </c>
       <c r="J59" s="4" t="s">
-        <v>406</v>
-      </c>
-      <c r="K59" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L59" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="60" s="1" customFormat="1" ht="63.75" spans="1:12">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="60" s="1" customFormat="1" ht="63.75" spans="1:10">
       <c r="A60" s="1" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>12</v>
@@ -8349,25 +7923,19 @@
       <c r="F60" s="1">
         <v>5</v>
       </c>
-      <c r="I60" s="1" t="s">
-        <v>244</v>
+      <c r="I60" s="4" t="s">
+        <v>406</v>
       </c>
       <c r="J60" s="4" t="s">
-        <v>408</v>
-      </c>
-      <c r="K60" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L60" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="61" s="1" customFormat="1" ht="63.75" spans="1:12">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="61" s="1" customFormat="1" ht="63.75" spans="1:10">
       <c r="A61" s="1" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>12</v>
@@ -8381,25 +7949,19 @@
       <c r="F61" s="1">
         <v>5</v>
       </c>
-      <c r="I61" s="1" t="s">
-        <v>244</v>
+      <c r="I61" s="4" t="s">
+        <v>408</v>
       </c>
       <c r="J61" s="4" t="s">
-        <v>410</v>
-      </c>
-      <c r="K61" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L61" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="62" s="1" customFormat="1" ht="63.75" spans="1:12">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="62" s="1" customFormat="1" ht="63.75" spans="1:10">
       <c r="A62" s="1" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>12</v>
@@ -8413,25 +7975,19 @@
       <c r="F62" s="1">
         <v>5</v>
       </c>
-      <c r="I62" s="1" t="s">
-        <v>244</v>
+      <c r="I62" s="4" t="s">
+        <v>410</v>
       </c>
       <c r="J62" s="4" t="s">
-        <v>412</v>
-      </c>
-      <c r="K62" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L62" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="63" s="1" customFormat="1" ht="63.75" spans="1:12">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="63" s="1" customFormat="1" ht="63.75" spans="1:10">
       <c r="A63" s="1" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>12</v>
@@ -8445,25 +8001,19 @@
       <c r="F63" s="1">
         <v>5</v>
       </c>
-      <c r="I63" s="1" t="s">
-        <v>244</v>
+      <c r="I63" s="4" t="s">
+        <v>412</v>
       </c>
       <c r="J63" s="4" t="s">
-        <v>414</v>
-      </c>
-      <c r="K63" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L63" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="64" s="1" customFormat="1" ht="63.75" spans="1:12">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="64" s="1" customFormat="1" ht="63.75" spans="1:10">
       <c r="A64" s="1" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>12</v>
@@ -8477,25 +8027,19 @@
       <c r="F64" s="1">
         <v>5</v>
       </c>
-      <c r="I64" s="1" t="s">
-        <v>244</v>
+      <c r="I64" s="4" t="s">
+        <v>414</v>
       </c>
       <c r="J64" s="4" t="s">
-        <v>416</v>
-      </c>
-      <c r="K64" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L64" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="65" s="1" customFormat="1" ht="63.75" spans="1:12">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="65" s="1" customFormat="1" ht="63.75" spans="1:10">
       <c r="A65" s="1" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>12</v>
@@ -8509,25 +8053,19 @@
       <c r="F65" s="1">
         <v>5</v>
       </c>
-      <c r="I65" s="1" t="s">
-        <v>244</v>
+      <c r="I65" s="4" t="s">
+        <v>416</v>
       </c>
       <c r="J65" s="4" t="s">
-        <v>418</v>
-      </c>
-      <c r="K65" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L65" s="4" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="66" s="1" customFormat="1" ht="63.75" spans="1:12">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="66" s="1" customFormat="1" ht="63.75" spans="1:10">
       <c r="A66" s="1" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>12</v>
@@ -8541,17 +8079,11 @@
       <c r="F66" s="1">
         <v>5</v>
       </c>
-      <c r="I66" s="1" t="s">
-        <v>244</v>
+      <c r="I66" s="4" t="s">
+        <v>418</v>
       </c>
       <c r="J66" s="4" t="s">
-        <v>420</v>
-      </c>
-      <c r="K66" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="L66" s="4" t="s">
-        <v>247</v>
+        <v>322</v>
       </c>
     </row>
   </sheetData>
